--- a/Data/BDD_IQS_Person.xlsx
+++ b/Data/BDD_IQS_Person.xlsx
@@ -6,15 +6,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1005" yWindow="-120" windowWidth="27915" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="3" d3p1:id="rId5"/>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="4" d3p1:id="rId6"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="17" d3p1:id="rId19"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="18" d3p1:id="rId20"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="2142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="2156">
   <si>
     <t>Id</t>
   </si>
@@ -4546,6 +4546,33 @@
     <t>+33767987409</t>
   </si>
   <si>
+    <t>P00185</t>
+  </si>
+  <si>
+    <t>ELIYEL</t>
+  </si>
+  <si>
+    <t>KHOURY-RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>M00081:15;M00082:35;M00067:50</t>
+  </si>
+  <si>
+    <t>1220237019</t>
+  </si>
+  <si>
+    <t>de l’Eglise</t>
+  </si>
+  <si>
+    <t>93340</t>
+  </si>
+  <si>
+    <t>Le Raincy</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
     <t>Designation</t>
   </si>
   <si>
@@ -6433,13 +6460,28 @@
     <t>De Lyon</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Landry Wilson Sourou</t>
   </si>
   <si>
     <t>AGONHOUMEY</t>
+  </si>
+  <si>
+    <t>M00082</t>
+  </si>
+  <si>
+    <t>LE PACTE PUBLISHING</t>
+  </si>
+  <si>
+    <t>1000 €</t>
+  </si>
+  <si>
+    <t>944404086</t>
+  </si>
+  <si>
+    <t>De Ponthieu</t>
+  </si>
+  <si>
+    <t>khouryandy@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -6757,9 +6799,9 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V185"/>
+  <dimension ref="A1:V186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19342,14 +19384,82 @@
         <v>28</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="0" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B186" s="0" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C186" s="0" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D186" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="E186" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F186" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G186" s="0" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H186" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="I186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="J186" s="0" t="s">
+        <v>1514</v>
+      </c>
+      <c r="K186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="L186" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="M186" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="N186" s="0" t="s">
+        <v>1515</v>
+      </c>
+      <c r="O186" s="0" t="s">
+        <v>1516</v>
+      </c>
+      <c r="P186" s="0" t="s">
+        <v>1517</v>
+      </c>
+      <c r="Q186" s="0" t="s">
+        <v>1518</v>
+      </c>
+      <c r="R186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="T186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="U186" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="V186" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19357,7 +19467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -19369,16 +19479,16 @@
         <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>11</v>
@@ -19399,13 +19509,13 @@
         <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>17</v>
@@ -19419,7 +19529,7 @@
         <v>620</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>27</v>
@@ -19428,19 +19538,19 @@
         <v>28</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>374</v>
@@ -19461,13 +19571,13 @@
         <v>48</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>1523</v>
+        <v>1532</v>
       </c>
       <c r="Q2" s="0" t="s">
         <v>518</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>623</v>
@@ -19478,40 +19588,40 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1525</v>
+        <v>1534</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1526</v>
+        <v>1535</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1064</v>
@@ -19523,16 +19633,16 @@
         <v>48</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>1532</v>
+        <v>1541</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>1533</v>
+        <v>1542</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>1535</v>
+        <v>1544</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>28</v>
@@ -19540,10 +19650,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1536</v>
+        <v>1545</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1537</v>
+        <v>1546</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>27</v>
@@ -19552,19 +19662,19 @@
         <v>28</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>1539</v>
+        <v>1548</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1540</v>
+        <v>1549</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>218</v>
@@ -19573,7 +19683,7 @@
         <v>57</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>1541</v>
+        <v>1550</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>69</v>
@@ -19588,13 +19698,13 @@
         <v>1110</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>1542</v>
+        <v>1551</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>1543</v>
+        <v>1552</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>28</v>
@@ -19602,10 +19712,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1545</v>
+        <v>1554</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>27</v>
@@ -19614,10 +19724,10 @@
         <v>28</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>1546</v>
+        <v>1555</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1547</v>
+        <v>1556</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>28</v>
@@ -19626,25 +19736,25 @@
         <v>28</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1548</v>
+        <v>1557</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>1549</v>
+        <v>1558</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>1551</v>
+        <v>1560</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>28</v>
@@ -19656,18 +19766,18 @@
         <v>28</v>
       </c>
       <c r="S5" s="0" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>27</v>
@@ -19676,19 +19786,19 @@
         <v>28</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>1559</v>
+        <v>1568</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="H6" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1561</v>
+        <v>1570</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>756</v>
@@ -19697,7 +19807,7 @@
         <v>57</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>163</v>
@@ -19709,16 +19819,16 @@
         <v>48</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S6" s="0" t="s">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="T6" s="0" t="s">
         <v>28</v>
@@ -19726,10 +19836,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1566</v>
+        <v>1575</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1567</v>
+        <v>1576</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>27</v>
@@ -19738,28 +19848,28 @@
         <v>28</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>1568</v>
+        <v>1577</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>1569</v>
+        <v>1578</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>448</v>
@@ -19771,16 +19881,16 @@
         <v>48</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>1573</v>
+        <v>1582</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="R7" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="T7" s="0" t="s">
         <v>28</v>
@@ -19791,7 +19901,7 @@
         <v>1128</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1576</v>
+        <v>1585</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>27</v>
@@ -19800,19 +19910,19 @@
         <v>28</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H8" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1580</v>
+        <v>1589</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>1447</v>
@@ -19821,7 +19931,7 @@
         <v>312</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>1581</v>
+        <v>1590</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>350</v>
@@ -19836,16 +19946,16 @@
         <v>1187</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>1582</v>
+        <v>1591</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>1584</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="9">
@@ -19853,7 +19963,7 @@
         <v>934</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>27</v>
@@ -19862,22 +19972,22 @@
         <v>28</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H9" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="K9" s="0" t="s">
         <v>57</v>
@@ -19886,25 +19996,25 @@
         <v>393</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>1591</v>
+        <v>1600</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>1592</v>
+        <v>1601</v>
       </c>
       <c r="O9" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>1593</v>
+        <v>1602</v>
       </c>
       <c r="Q9" s="0" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>1595</v>
+        <v>1604</v>
       </c>
       <c r="T9" s="0" t="s">
         <v>28</v>
@@ -19912,10 +20022,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1597</v>
+        <v>1606</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>27</v>
@@ -19927,16 +20037,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1599</v>
+        <v>1608</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>1464</v>
@@ -19945,39 +20055,39 @@
         <v>57</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>1600</v>
+        <v>1609</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1079</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>1601</v>
+        <v>1610</v>
       </c>
       <c r="O10" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="Q10" s="0" t="s">
-        <v>1603</v>
+        <v>1612</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="T10" s="0" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1606</v>
+        <v>1615</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>27</v>
@@ -19989,7 +20099,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>28</v>
@@ -19998,7 +20108,7 @@
         <v>28</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>971</v>
@@ -20007,7 +20117,7 @@
         <v>57</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>1610</v>
+        <v>1619</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>911</v>
@@ -20028,7 +20138,7 @@
         <v>28</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>1611</v>
+        <v>1620</v>
       </c>
       <c r="T11" s="0" t="s">
         <v>28</v>
@@ -20039,7 +20149,7 @@
         <v>446</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1612</v>
+        <v>1621</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>27</v>
@@ -20048,46 +20158,46 @@
         <v>28</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>1613</v>
+        <v>1622</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1614</v>
+        <v>1623</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>426</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>1616</v>
+        <v>1625</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>656</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="O12" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>1618</v>
+        <v>1627</v>
       </c>
       <c r="Q12" s="0" t="s">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S12" s="0" t="s">
         <v>449</v>
@@ -20098,10 +20208,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>27</v>
@@ -20113,7 +20223,7 @@
         <v>28</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>28</v>
@@ -20122,16 +20232,16 @@
         <v>28</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1622</v>
+        <v>1631</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>1623</v>
+        <v>1632</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>911</v>
@@ -20143,16 +20253,16 @@
         <v>48</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>1625</v>
+        <v>1634</v>
       </c>
       <c r="Q13" s="0" t="s">
-        <v>1626</v>
+        <v>1635</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>1627</v>
+        <v>1636</v>
       </c>
       <c r="T13" s="0" t="s">
         <v>28</v>
@@ -20160,10 +20270,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1628</v>
+        <v>1637</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1629</v>
+        <v>1638</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>27</v>
@@ -20175,7 +20285,7 @@
         <v>28</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>28</v>
@@ -20184,37 +20294,37 @@
         <v>1041</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>1634</v>
+        <v>1643</v>
       </c>
       <c r="O14" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>1635</v>
+        <v>1644</v>
       </c>
       <c r="Q14" s="0" t="s">
-        <v>1636</v>
+        <v>1645</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>1637</v>
+        <v>1646</v>
       </c>
       <c r="T14" s="0" t="s">
         <v>28</v>
@@ -20222,10 +20332,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1639</v>
+        <v>1648</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>27</v>
@@ -20237,46 +20347,46 @@
         <v>28</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>562</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1640</v>
+        <v>1649</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>1641</v>
+        <v>1650</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>1642</v>
+        <v>1651</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>1643</v>
+        <v>1652</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="O15" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="Q15" s="0" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="T15" s="0" t="s">
         <v>28</v>
@@ -20284,10 +20394,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>1648</v>
+        <v>1657</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1649</v>
+        <v>1658</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>27</v>
@@ -20296,46 +20406,46 @@
         <v>28</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1651</v>
+        <v>1660</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1652</v>
+        <v>1661</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>1653</v>
+        <v>1662</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>1656</v>
+        <v>1665</v>
       </c>
       <c r="O16" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="Q16" s="0" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="R16" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S16" s="0" t="s">
         <v>28</v>
@@ -20349,7 +20459,7 @@
         <v>1454</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>27</v>
@@ -20358,19 +20468,19 @@
         <v>1455</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="0" t="s">
         <v>1660</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G17" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>1651</v>
-      </c>
       <c r="I17" s="0" t="s">
-        <v>1661</v>
+        <v>1670</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>971</v>
@@ -20382,10 +20492,10 @@
         <v>1249</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>1662</v>
+        <v>1671</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>1663</v>
+        <v>1672</v>
       </c>
       <c r="O17" s="0" t="s">
         <v>48</v>
@@ -20394,7 +20504,7 @@
         <v>1453</v>
       </c>
       <c r="Q17" s="0" t="s">
-        <v>1664</v>
+        <v>1673</v>
       </c>
       <c r="R17" s="0" t="s">
         <v>28</v>
@@ -20408,10 +20518,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>1665</v>
+        <v>1674</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>27</v>
@@ -20420,19 +20530,19 @@
         <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>1667</v>
+        <v>1676</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H18" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1668</v>
+        <v>1677</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>520</v>
@@ -20441,7 +20551,7 @@
         <v>57</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>1669</v>
+        <v>1678</v>
       </c>
       <c r="M18" s="0" t="s">
         <v>448</v>
@@ -20456,13 +20566,13 @@
         <v>566</v>
       </c>
       <c r="Q18" s="0" t="s">
-        <v>1670</v>
+        <v>1679</v>
       </c>
       <c r="R18" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>1671</v>
+        <v>1680</v>
       </c>
       <c r="T18" s="0" t="s">
         <v>28</v>
@@ -20473,7 +20583,7 @@
         <v>817</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>27</v>
@@ -20485,16 +20595,16 @@
         <v>28</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1674</v>
+        <v>1683</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>274</v>
@@ -20503,28 +20613,28 @@
         <v>411</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="N19" s="0" t="s">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="O19" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>1678</v>
+        <v>1687</v>
       </c>
       <c r="Q19" s="0" t="s">
-        <v>1679</v>
+        <v>1688</v>
       </c>
       <c r="R19" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S19" s="0" t="s">
-        <v>1680</v>
+        <v>1689</v>
       </c>
       <c r="T19" s="0" t="s">
         <v>28</v>
@@ -20532,10 +20642,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>1681</v>
+        <v>1690</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1682</v>
+        <v>1691</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>27</v>
@@ -20547,16 +20657,16 @@
         <v>28</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>1683</v>
+        <v>1692</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1684</v>
+        <v>1693</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1685</v>
+        <v>1694</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>654</v>
@@ -20568,36 +20678,36 @@
         <v>219</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>1686</v>
+        <v>1695</v>
       </c>
       <c r="N20" s="0" t="s">
-        <v>1687</v>
+        <v>1696</v>
       </c>
       <c r="O20" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>1688</v>
+        <v>1697</v>
       </c>
       <c r="Q20" s="0" t="s">
-        <v>1689</v>
+        <v>1698</v>
       </c>
       <c r="R20" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S20" s="0" t="s">
         <v>28</v>
       </c>
       <c r="T20" s="0" t="s">
-        <v>1690</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1692</v>
+        <v>1701</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>27</v>
@@ -20606,10 +20716,10 @@
         <v>28</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>1693</v>
+        <v>1702</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G21" s="0" t="s">
         <v>28</v>
@@ -20627,7 +20737,7 @@
         <v>57</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>1694</v>
+        <v>1703</v>
       </c>
       <c r="M21" s="0" t="s">
         <v>172</v>
@@ -20645,7 +20755,7 @@
         <v>28</v>
       </c>
       <c r="R21" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S21" s="0" t="s">
         <v>1424</v>
@@ -20659,7 +20769,7 @@
         <v>343</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1695</v>
+        <v>1704</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>27</v>
@@ -20668,28 +20778,28 @@
         <v>28</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>1696</v>
+        <v>1705</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1698</v>
+        <v>1707</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>1700</v>
+        <v>1709</v>
       </c>
       <c r="M22" s="0" t="s">
         <v>338</v>
@@ -20707,7 +20817,7 @@
         <v>342</v>
       </c>
       <c r="R22" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S22" s="0" t="s">
         <v>344</v>
@@ -20721,7 +20831,7 @@
         <v>273</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1701</v>
+        <v>1710</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>27</v>
@@ -20730,34 +20840,34 @@
         <v>28</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>1702</v>
+        <v>1711</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1703</v>
+        <v>1712</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1704</v>
+        <v>1713</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>28</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>1707</v>
+        <v>1716</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>1708</v>
+        <v>1717</v>
       </c>
       <c r="O23" s="0" t="s">
         <v>48</v>
@@ -20766,13 +20876,13 @@
         <v>381</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>1709</v>
+        <v>1718</v>
       </c>
       <c r="R23" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>1710</v>
+        <v>1719</v>
       </c>
       <c r="T23" s="0" t="s">
         <v>28</v>
@@ -20783,58 +20893,58 @@
         <v>87</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>1713</v>
+        <v>1722</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G24" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>1716</v>
+        <v>1725</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="O24" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>1720</v>
+        <v>1729</v>
       </c>
       <c r="R24" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S24" s="0" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="T24" s="0" t="s">
         <v>28</v>
@@ -20842,40 +20952,40 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1723</v>
+        <v>1732</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>1724</v>
+        <v>1733</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>1725</v>
+        <v>1734</v>
       </c>
       <c r="H25" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1726</v>
+        <v>1735</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="M25" s="0" t="s">
         <v>1064</v>
@@ -20887,16 +20997,16 @@
         <v>48</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>1727</v>
+        <v>1736</v>
       </c>
       <c r="Q25" s="0" t="s">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="R25" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="T25" s="0" t="s">
         <v>28</v>
@@ -20907,7 +21017,7 @@
         <v>372</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1730</v>
+        <v>1739</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>27</v>
@@ -20916,28 +21026,28 @@
         <v>28</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>1731</v>
+        <v>1740</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1733</v>
+        <v>1742</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1734</v>
+        <v>1743</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>1735</v>
+        <v>1744</v>
       </c>
       <c r="M26" s="0" t="s">
         <v>448</v>
@@ -20955,7 +21065,7 @@
         <v>370</v>
       </c>
       <c r="R26" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S26" s="0" t="s">
         <v>377</v>
@@ -20969,7 +21079,7 @@
         <v>207</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1736</v>
+        <v>1745</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>27</v>
@@ -20999,16 +21109,16 @@
         <v>28</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>1737</v>
+        <v>1746</v>
       </c>
       <c r="M27" s="0" t="s">
         <v>211</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>1738</v>
+        <v>1747</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>1739</v>
+        <v>1748</v>
       </c>
       <c r="P27" s="0" t="s">
         <v>206</v>
@@ -21017,7 +21127,7 @@
         <v>205</v>
       </c>
       <c r="R27" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S27" s="0" t="s">
         <v>213</v>
@@ -21031,7 +21141,7 @@
         <v>1410</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>27</v>
@@ -21040,10 +21150,10 @@
         <v>28</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>1741</v>
+        <v>1750</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="G28" s="0" t="s">
         <v>28</v>
@@ -21052,7 +21162,7 @@
         <v>995</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1743</v>
+        <v>1752</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>56</v>
@@ -21079,7 +21189,7 @@
         <v>1408</v>
       </c>
       <c r="R28" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S28" s="0" t="s">
         <v>1415</v>
@@ -21090,10 +21200,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>1744</v>
+        <v>1753</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1745</v>
+        <v>1754</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>27</v>
@@ -21102,19 +21212,19 @@
         <v>28</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>1746</v>
+        <v>1755</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1747</v>
+        <v>1756</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>587</v>
@@ -21123,13 +21233,13 @@
         <v>358</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="M29" s="0" t="s">
         <v>901</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>1750</v>
+        <v>1759</v>
       </c>
       <c r="O29" s="0" t="s">
         <v>48</v>
@@ -21138,13 +21248,13 @@
         <v>310</v>
       </c>
       <c r="Q29" s="0" t="s">
-        <v>1751</v>
+        <v>1760</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S29" s="0" t="s">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="T29" s="0" t="s">
         <v>28</v>
@@ -21155,7 +21265,7 @@
         <v>471</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1753</v>
+        <v>1762</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>27</v>
@@ -21164,19 +21274,19 @@
         <v>28</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>1755</v>
+        <v>1764</v>
       </c>
       <c r="H30" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>218</v>
@@ -21185,7 +21295,7 @@
         <v>123</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="M30" s="0" t="s">
         <v>440</v>
@@ -21197,13 +21307,13 @@
         <v>48</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>1758</v>
+        <v>1767</v>
       </c>
       <c r="Q30" s="0" t="s">
-        <v>1759</v>
+        <v>1768</v>
       </c>
       <c r="R30" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S30" s="0" t="s">
         <v>28</v>
@@ -21214,10 +21324,10 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>1760</v>
+        <v>1769</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1761</v>
+        <v>1770</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>27</v>
@@ -21226,19 +21336,19 @@
         <v>28</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>1762</v>
+        <v>1771</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1764</v>
+        <v>1773</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>294</v>
@@ -21247,7 +21357,7 @@
         <v>57</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>1765</v>
+        <v>1774</v>
       </c>
       <c r="M31" s="0" t="s">
         <v>1403</v>
@@ -21259,27 +21369,27 @@
         <v>48</v>
       </c>
       <c r="P31" s="0" t="s">
-        <v>1766</v>
+        <v>1775</v>
       </c>
       <c r="Q31" s="0" t="s">
-        <v>1767</v>
+        <v>1776</v>
       </c>
       <c r="R31" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S31" s="0" t="s">
         <v>28</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>1768</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>1769</v>
+        <v>1778</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1770</v>
+        <v>1779</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>27</v>
@@ -21288,19 +21398,19 @@
         <v>28</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>1771</v>
+        <v>1780</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="H32" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>828</v>
@@ -21309,10 +21419,10 @@
         <v>57</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>1774</v>
+        <v>1783</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>1775</v>
+        <v>1784</v>
       </c>
       <c r="N32" s="0" t="s">
         <v>70</v>
@@ -21321,16 +21431,16 @@
         <v>48</v>
       </c>
       <c r="P32" s="0" t="s">
-        <v>1776</v>
+        <v>1785</v>
       </c>
       <c r="Q32" s="0" t="s">
-        <v>1777</v>
+        <v>1786</v>
       </c>
       <c r="R32" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S32" s="0" t="s">
-        <v>1778</v>
+        <v>1787</v>
       </c>
       <c r="T32" s="0" t="s">
         <v>28</v>
@@ -21341,7 +21451,7 @@
         <v>120</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>27</v>
@@ -21350,19 +21460,19 @@
         <v>28</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>597</v>
@@ -21371,7 +21481,7 @@
         <v>57</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="M33" s="0" t="s">
         <v>1224</v>
@@ -21383,16 +21493,16 @@
         <v>48</v>
       </c>
       <c r="P33" s="0" t="s">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="Q33" s="0" t="s">
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="R33" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S33" s="0" t="s">
-        <v>1786</v>
+        <v>1795</v>
       </c>
       <c r="T33" s="0" t="s">
         <v>28</v>
@@ -21400,31 +21510,31 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>1787</v>
+        <v>1796</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1788</v>
+        <v>1797</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>1789</v>
+        <v>1798</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1791</v>
+        <v>1800</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>218</v>
@@ -21433,13 +21543,13 @@
         <v>57</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>1792</v>
+        <v>1801</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="O34" s="0" t="s">
         <v>48</v>
@@ -21448,13 +21558,13 @@
         <v>470</v>
       </c>
       <c r="Q34" s="0" t="s">
-        <v>1795</v>
+        <v>1804</v>
       </c>
       <c r="R34" s="0" t="s">
-        <v>1796</v>
+        <v>1805</v>
       </c>
       <c r="S34" s="0" t="s">
-        <v>1797</v>
+        <v>1806</v>
       </c>
       <c r="T34" s="0" t="s">
         <v>28</v>
@@ -21462,10 +21572,10 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>1798</v>
+        <v>1807</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1799</v>
+        <v>1808</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>27</v>
@@ -21474,19 +21584,19 @@
         <v>28</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>1800</v>
+        <v>1809</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>1801</v>
+        <v>1810</v>
       </c>
       <c r="H35" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1802</v>
+        <v>1811</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>819</v>
@@ -21495,7 +21605,7 @@
         <v>57</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>1803</v>
+        <v>1812</v>
       </c>
       <c r="M35" s="0" t="s">
         <v>350</v>
@@ -21507,16 +21617,16 @@
         <v>48</v>
       </c>
       <c r="P35" s="0" t="s">
-        <v>1804</v>
+        <v>1813</v>
       </c>
       <c r="Q35" s="0" t="s">
-        <v>1805</v>
+        <v>1814</v>
       </c>
       <c r="R35" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S35" s="0" t="s">
-        <v>1806</v>
+        <v>1815</v>
       </c>
       <c r="T35" s="0" t="s">
         <v>28</v>
@@ -21524,10 +21634,10 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>1807</v>
+        <v>1816</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1808</v>
+        <v>1817</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>27</v>
@@ -21536,19 +21646,19 @@
         <v>28</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>1809</v>
+        <v>1818</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H36" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>303</v>
@@ -21557,28 +21667,28 @@
         <v>57</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>1811</v>
+        <v>1820</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>1812</v>
+        <v>1821</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>1813</v>
+        <v>1822</v>
       </c>
       <c r="O36" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P36" s="0" t="s">
-        <v>1814</v>
+        <v>1823</v>
       </c>
       <c r="Q36" s="0" t="s">
-        <v>1815</v>
+        <v>1824</v>
       </c>
       <c r="R36" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S36" s="0" t="s">
-        <v>1816</v>
+        <v>1825</v>
       </c>
       <c r="T36" s="0" t="s">
         <v>28</v>
@@ -21586,10 +21696,10 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>1817</v>
+        <v>1826</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1818</v>
+        <v>1827</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>27</v>
@@ -21598,19 +21708,19 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>1819</v>
+        <v>1828</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>1820</v>
+        <v>1829</v>
       </c>
       <c r="H37" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1821</v>
+        <v>1830</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>56</v>
@@ -21619,10 +21729,10 @@
         <v>57</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>1822</v>
+        <v>1831</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N37" s="0" t="s">
         <v>70</v>
@@ -21631,16 +21741,16 @@
         <v>48</v>
       </c>
       <c r="P37" s="0" t="s">
-        <v>1824</v>
+        <v>1833</v>
       </c>
       <c r="Q37" s="0" t="s">
-        <v>1825</v>
+        <v>1834</v>
       </c>
       <c r="R37" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S37" s="0" t="s">
-        <v>1826</v>
+        <v>1835</v>
       </c>
       <c r="T37" s="0" t="s">
         <v>28</v>
@@ -21648,10 +21758,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>1827</v>
+        <v>1836</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1828</v>
+        <v>1837</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>27</v>
@@ -21663,16 +21773,16 @@
         <v>28</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H38" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1829</v>
+        <v>1838</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>587</v>
@@ -21681,10 +21791,10 @@
         <v>57</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>1830</v>
+        <v>1839</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>70</v>
@@ -21696,16 +21806,16 @@
         <v>187</v>
       </c>
       <c r="Q38" s="0" t="s">
-        <v>1831</v>
+        <v>1840</v>
       </c>
       <c r="R38" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S38" s="0" t="s">
-        <v>1832</v>
+        <v>1841</v>
       </c>
       <c r="T38" s="0" t="s">
-        <v>1833</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="39">
@@ -21713,7 +21823,7 @@
         <v>491</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1834</v>
+        <v>1843</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>27</v>
@@ -21722,19 +21832,19 @@
         <v>28</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>1835</v>
+        <v>1844</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H39" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>1836</v>
+        <v>1845</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>587</v>
@@ -21743,10 +21853,10 @@
         <v>57</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>1830</v>
+        <v>1839</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N39" s="0" t="s">
         <v>70</v>
@@ -21761,10 +21871,10 @@
         <v>489</v>
       </c>
       <c r="R39" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S39" s="0" t="s">
-        <v>1837</v>
+        <v>1846</v>
       </c>
       <c r="T39" s="0" t="s">
         <v>28</v>
@@ -21775,7 +21885,7 @@
         <v>880</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1838</v>
+        <v>1847</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>27</v>
@@ -21784,19 +21894,19 @@
         <v>28</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>1839</v>
+        <v>1848</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>1840</v>
+        <v>1849</v>
       </c>
       <c r="H40" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>1841</v>
+        <v>1850</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>111</v>
@@ -21805,10 +21915,10 @@
         <v>57</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>1842</v>
+        <v>1851</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N40" s="0" t="s">
         <v>70</v>
@@ -21817,13 +21927,13 @@
         <v>48</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>1843</v>
+        <v>1852</v>
       </c>
       <c r="Q40" s="0" t="s">
-        <v>1844</v>
+        <v>1853</v>
       </c>
       <c r="R40" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S40" s="0" t="s">
         <v>28</v>
@@ -21834,10 +21944,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>1845</v>
+        <v>1854</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1846</v>
+        <v>1855</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>27</v>
@@ -21849,13 +21959,13 @@
         <v>28</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="I41" s="0" t="s">
         <v>28</v>
@@ -21867,39 +21977,39 @@
         <v>57</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>1848</v>
+        <v>1857</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>1849</v>
+        <v>1858</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="O41" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P41" s="0" t="s">
-        <v>1850</v>
+        <v>1859</v>
       </c>
       <c r="Q41" s="0" t="s">
-        <v>1851</v>
+        <v>1860</v>
       </c>
       <c r="R41" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S41" s="0" t="s">
-        <v>1852</v>
+        <v>1861</v>
       </c>
       <c r="T41" s="0" t="s">
-        <v>1853</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>1854</v>
+        <v>1863</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1855</v>
+        <v>1864</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>27</v>
@@ -21908,19 +22018,19 @@
         <v>28</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>1856</v>
+        <v>1865</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>1857</v>
+        <v>1866</v>
       </c>
       <c r="H42" s="0" t="s">
         <v>785</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>1858</v>
+        <v>1867</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>828</v>
@@ -21929,28 +22039,28 @@
         <v>57</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>1859</v>
+        <v>1868</v>
       </c>
       <c r="M42" s="0" t="s">
-        <v>1860</v>
+        <v>1869</v>
       </c>
       <c r="N42" s="0" t="s">
-        <v>1861</v>
+        <v>1870</v>
       </c>
       <c r="O42" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P42" s="0" t="s">
-        <v>1862</v>
+        <v>1871</v>
       </c>
       <c r="Q42" s="0" t="s">
-        <v>1863</v>
+        <v>1872</v>
       </c>
       <c r="R42" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S42" s="0" t="s">
-        <v>1864</v>
+        <v>1873</v>
       </c>
       <c r="T42" s="0" t="s">
         <v>28</v>
@@ -21958,10 +22068,10 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>1865</v>
+        <v>1874</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1866</v>
+        <v>1875</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>27</v>
@@ -21970,28 +22080,28 @@
         <v>28</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>1867</v>
+        <v>1876</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H43" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>1868</v>
+        <v>1877</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>1870</v>
+        <v>1879</v>
       </c>
       <c r="M43" s="0" t="s">
         <v>448</v>
@@ -22003,16 +22113,16 @@
         <v>48</v>
       </c>
       <c r="P43" s="0" t="s">
-        <v>1871</v>
+        <v>1880</v>
       </c>
       <c r="Q43" s="0" t="s">
-        <v>1872</v>
+        <v>1881</v>
       </c>
       <c r="R43" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S43" s="0" t="s">
-        <v>1873</v>
+        <v>1882</v>
       </c>
       <c r="T43" s="0" t="s">
         <v>28</v>
@@ -22023,37 +22133,37 @@
         <v>178</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1874</v>
+        <v>1883</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>1876</v>
+        <v>1885</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>1878</v>
+        <v>1887</v>
       </c>
       <c r="K44" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>1879</v>
+        <v>1888</v>
       </c>
       <c r="M44" s="0" t="s">
         <v>172</v>
@@ -22068,13 +22178,13 @@
         <v>435</v>
       </c>
       <c r="Q44" s="0" t="s">
-        <v>1880</v>
+        <v>1889</v>
       </c>
       <c r="R44" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S44" s="0" t="s">
-        <v>1881</v>
+        <v>1890</v>
       </c>
       <c r="T44" s="0" t="s">
         <v>28</v>
@@ -22085,7 +22195,7 @@
         <v>232</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1882</v>
+        <v>1891</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>27</v>
@@ -22094,28 +22204,28 @@
         <v>28</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>1883</v>
+        <v>1892</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>1885</v>
+        <v>1894</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>1886</v>
+        <v>1895</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>1887</v>
+        <v>1896</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>1888</v>
+        <v>1897</v>
       </c>
       <c r="M45" s="0" t="s">
         <v>911</v>
@@ -22127,16 +22237,16 @@
         <v>48</v>
       </c>
       <c r="P45" s="0" t="s">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="Q45" s="0" t="s">
-        <v>1890</v>
+        <v>1899</v>
       </c>
       <c r="R45" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S45" s="0" t="s">
-        <v>1891</v>
+        <v>1900</v>
       </c>
       <c r="T45" s="0" t="s">
         <v>28</v>
@@ -22144,10 +22254,10 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>1892</v>
+        <v>1901</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1893</v>
+        <v>1902</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>27</v>
@@ -22156,49 +22266,49 @@
         <v>28</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>1894</v>
+        <v>1903</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H46" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>1895</v>
+        <v>1904</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>1820</v>
+        <v>1829</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>1896</v>
+        <v>1905</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>1897</v>
+        <v>1906</v>
       </c>
       <c r="M46" s="0" t="s">
-        <v>1898</v>
+        <v>1907</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>1899</v>
+        <v>1908</v>
       </c>
       <c r="O46" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P46" s="0" t="s">
-        <v>1900</v>
+        <v>1909</v>
       </c>
       <c r="Q46" s="0" t="s">
-        <v>1901</v>
+        <v>1910</v>
       </c>
       <c r="R46" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S46" s="0" t="s">
-        <v>1902</v>
+        <v>1911</v>
       </c>
       <c r="T46" s="0" t="s">
         <v>28</v>
@@ -22206,10 +22316,10 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>1903</v>
+        <v>1912</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>1904</v>
+        <v>1913</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>27</v>
@@ -22218,49 +22328,49 @@
         <v>28</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>1905</v>
+        <v>1914</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="G47" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>1906</v>
+        <v>1915</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>1907</v>
+        <v>1916</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>1734</v>
+        <v>1743</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>1908</v>
+        <v>1917</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="N47" s="0" t="s">
-        <v>1906</v>
+        <v>1915</v>
       </c>
       <c r="O47" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P47" s="0" t="s">
-        <v>1573</v>
+        <v>1582</v>
       </c>
       <c r="Q47" s="0" t="s">
-        <v>1910</v>
+        <v>1919</v>
       </c>
       <c r="R47" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="0" t="s">
-        <v>1911</v>
+        <v>1920</v>
       </c>
       <c r="T47" s="0" t="s">
         <v>28</v>
@@ -22271,7 +22381,7 @@
         <v>754</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>1912</v>
+        <v>1921</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>27</v>
@@ -22280,19 +22390,19 @@
         <v>28</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>1913</v>
+        <v>1922</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>1914</v>
+        <v>1923</v>
       </c>
       <c r="H48" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>1915</v>
+        <v>1924</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>111</v>
@@ -22301,7 +22411,7 @@
         <v>57</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>1916</v>
+        <v>1925</v>
       </c>
       <c r="M48" s="0" t="s">
         <v>428</v>
@@ -22322,7 +22432,7 @@
         <v>28</v>
       </c>
       <c r="S48" s="0" t="s">
-        <v>1917</v>
+        <v>1926</v>
       </c>
       <c r="T48" s="0" t="s">
         <v>28</v>
@@ -22330,10 +22440,10 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>1918</v>
+        <v>1927</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>1919</v>
+        <v>1928</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>27</v>
@@ -22342,49 +22452,49 @@
         <v>28</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>1920</v>
+        <v>1929</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G49" s="0" t="s">
         <v>731</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>1922</v>
+        <v>1931</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>1923</v>
+        <v>1932</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>1924</v>
+        <v>1933</v>
       </c>
       <c r="M49" s="0" t="s">
-        <v>1925</v>
+        <v>1934</v>
       </c>
       <c r="N49" s="0" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="O49" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P49" s="0" t="s">
-        <v>1926</v>
+        <v>1935</v>
       </c>
       <c r="Q49" s="0" t="s">
-        <v>1927</v>
+        <v>1936</v>
       </c>
       <c r="R49" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S49" s="0" t="s">
-        <v>1928</v>
+        <v>1937</v>
       </c>
       <c r="T49" s="0" t="s">
         <v>28</v>
@@ -22392,10 +22502,10 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>1930</v>
+        <v>1939</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>27</v>
@@ -22407,7 +22517,7 @@
         <v>28</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G50" s="0" t="s">
         <v>731</v>
@@ -22416,16 +22526,16 @@
         <v>70</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>1931</v>
+        <v>1940</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>1869</v>
+        <v>1878</v>
       </c>
       <c r="K50" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>1932</v>
+        <v>1941</v>
       </c>
       <c r="M50" s="0" t="s">
         <v>1224</v>
@@ -22437,13 +22547,13 @@
         <v>48</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>1933</v>
+        <v>1942</v>
       </c>
       <c r="Q50" s="0" t="s">
-        <v>1934</v>
+        <v>1943</v>
       </c>
       <c r="R50" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S50" s="0" t="s">
         <v>28</v>
@@ -22457,7 +22567,7 @@
         <v>1365</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>1935</v>
+        <v>1944</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>27</v>
@@ -22469,16 +22579,16 @@
         <v>1077</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>1936</v>
+        <v>1945</v>
       </c>
       <c r="G51" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>1937</v>
+        <v>1946</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>1938</v>
+        <v>1947</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>828</v>
@@ -22487,10 +22597,10 @@
         <v>57</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>1939</v>
+        <v>1948</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>1940</v>
+        <v>1949</v>
       </c>
       <c r="N51" s="0" t="s">
         <v>1080</v>
@@ -22499,13 +22609,13 @@
         <v>48</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>1941</v>
+        <v>1950</v>
       </c>
       <c r="Q51" s="0" t="s">
         <v>1074</v>
       </c>
       <c r="R51" s="0" t="s">
-        <v>1942</v>
+        <v>1951</v>
       </c>
       <c r="S51" s="0" t="s">
         <v>1081</v>
@@ -22516,10 +22626,10 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>1943</v>
+        <v>1952</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>1944</v>
+        <v>1953</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>27</v>
@@ -22528,28 +22638,28 @@
         <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>1945</v>
+        <v>1954</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>1946</v>
+        <v>1955</v>
       </c>
       <c r="H52" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>1947</v>
+        <v>1956</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>1948</v>
+        <v>1957</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>1949</v>
+        <v>1958</v>
       </c>
       <c r="M52" s="0" t="s">
         <v>448</v>
@@ -22567,10 +22677,10 @@
         <v>28</v>
       </c>
       <c r="R52" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S52" s="0" t="s">
-        <v>1950</v>
+        <v>1959</v>
       </c>
       <c r="T52" s="0" t="s">
         <v>28</v>
@@ -22581,7 +22691,7 @@
         <v>1257</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>1951</v>
+        <v>1960</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>27</v>
@@ -22593,25 +22703,25 @@
         <v>28</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H53" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>1953</v>
+        <v>1962</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>1954</v>
+        <v>1963</v>
       </c>
       <c r="M53" s="0" t="s">
         <v>457</v>
@@ -22623,13 +22733,13 @@
         <v>48</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>1955</v>
+        <v>1964</v>
       </c>
       <c r="Q53" s="0" t="s">
         <v>1255</v>
       </c>
       <c r="R53" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S53" s="0" t="s">
         <v>1261</v>
@@ -22643,7 +22753,7 @@
         <v>109</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>1956</v>
+        <v>1965</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>27</v>
@@ -22652,19 +22762,19 @@
         <v>28</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>1957</v>
+        <v>1966</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H54" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>111</v>
@@ -22702,31 +22812,31 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>1959</v>
+        <v>1968</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>1960</v>
+        <v>1969</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>1961</v>
+        <v>1970</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="H55" s="0" t="s">
         <v>47</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>100</v>
@@ -22735,7 +22845,7 @@
         <v>837</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>1964</v>
+        <v>1973</v>
       </c>
       <c r="M55" s="0" t="s">
         <v>350</v>
@@ -22750,13 +22860,13 @@
         <v>1445</v>
       </c>
       <c r="Q55" s="0" t="s">
-        <v>1965</v>
+        <v>1974</v>
       </c>
       <c r="R55" s="0" t="s">
-        <v>1966</v>
+        <v>1975</v>
       </c>
       <c r="S55" s="0" t="s">
-        <v>1967</v>
+        <v>1976</v>
       </c>
       <c r="T55" s="0" t="s">
         <v>28</v>
@@ -22767,7 +22877,7 @@
         <v>636</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>1968</v>
+        <v>1977</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>27</v>
@@ -22776,7 +22886,7 @@
         <v>28</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>28</v>
@@ -22785,10 +22895,10 @@
         <v>28</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>1248</v>
@@ -22797,13 +22907,13 @@
         <v>57</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>1971</v>
+        <v>1980</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="O56" s="0" t="s">
         <v>48</v>
@@ -22812,13 +22922,13 @@
         <v>921</v>
       </c>
       <c r="Q56" s="0" t="s">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="R56" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S56" s="0" t="s">
-        <v>1974</v>
+        <v>1983</v>
       </c>
       <c r="T56" s="0" t="s">
         <v>28</v>
@@ -22826,10 +22936,10 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>27</v>
@@ -22841,7 +22951,7 @@
         <v>28</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G57" s="0" t="s">
         <v>28</v>
@@ -22850,16 +22960,16 @@
         <v>70</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>1978</v>
+        <v>1987</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="M57" s="0" t="s">
         <v>172</v>
@@ -22871,16 +22981,16 @@
         <v>48</v>
       </c>
       <c r="P57" s="0" t="s">
-        <v>1980</v>
+        <v>1989</v>
       </c>
       <c r="Q57" s="0" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="R57" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S57" s="0" t="s">
-        <v>1982</v>
+        <v>1991</v>
       </c>
       <c r="T57" s="0" t="s">
         <v>28</v>
@@ -22891,7 +23001,7 @@
         <v>99</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>27</v>
@@ -22903,28 +23013,28 @@
         <v>28</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>1885</v>
+        <v>1894</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>1986</v>
+        <v>1995</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N58" s="0" t="s">
         <v>70</v>
@@ -22953,7 +23063,7 @@
         <v>1370</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>1987</v>
+        <v>1996</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>27</v>
@@ -22962,19 +23072,19 @@
         <v>28</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>1988</v>
+        <v>1997</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="H59" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>1989</v>
+        <v>1998</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>303</v>
@@ -22983,10 +23093,10 @@
         <v>57</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="N59" s="0" t="s">
         <v>70</v>
@@ -22995,16 +23105,16 @@
         <v>48</v>
       </c>
       <c r="P59" s="0" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Q59" s="0" t="s">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="R59" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S59" s="0" t="s">
-        <v>1994</v>
+        <v>2003</v>
       </c>
       <c r="T59" s="0" t="s">
         <v>28</v>
@@ -23015,7 +23125,7 @@
         <v>76</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>27</v>
@@ -23027,16 +23137,16 @@
         <v>708</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>1996</v>
+        <v>2005</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>28</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>1997</v>
+        <v>2006</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>1112</v>
@@ -23045,10 +23155,10 @@
         <v>57</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N60" s="0" t="s">
         <v>70</v>
@@ -23057,16 +23167,16 @@
         <v>48</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="Q60" s="0" t="s">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="R60" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S60" s="0" t="s">
-        <v>1864</v>
+        <v>1873</v>
       </c>
       <c r="T60" s="0" t="s">
         <v>28</v>
@@ -23074,10 +23184,10 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="C61" s="0" t="s">
         <v>27</v>
@@ -23089,16 +23199,16 @@
         <v>28</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>731</v>
@@ -23107,13 +23217,13 @@
         <v>57</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="O61" s="0" t="s">
         <v>48</v>
@@ -23122,24 +23232,24 @@
         <v>231</v>
       </c>
       <c r="Q61" s="0" t="s">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="R61" s="0" t="s">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="S61" s="0" t="s">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="T61" s="0" t="s">
-        <v>2010</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C62" s="0" t="s">
         <v>27</v>
@@ -23148,19 +23258,19 @@
         <v>28</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>1539</v>
+        <v>1548</v>
       </c>
       <c r="H62" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>218</v>
@@ -23169,7 +23279,7 @@
         <v>57</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>1541</v>
+        <v>1550</v>
       </c>
       <c r="M62" s="0" t="s">
         <v>69</v>
@@ -23181,16 +23291,16 @@
         <v>48</v>
       </c>
       <c r="P62" s="0" t="s">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="Q62" s="0" t="s">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="R62" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S62" s="0" t="s">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="T62" s="0" t="s">
         <v>28</v>
@@ -23198,10 +23308,10 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>2018</v>
+        <v>2027</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>2019</v>
+        <v>2028</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>27</v>
@@ -23213,7 +23323,7 @@
         <v>28</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="G63" s="0" t="s">
         <v>28</v>
@@ -23222,7 +23332,7 @@
         <v>995</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>2020</v>
+        <v>2029</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>250</v>
@@ -23231,7 +23341,7 @@
         <v>512</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>2021</v>
+        <v>2030</v>
       </c>
       <c r="M63" s="0" t="s">
         <v>262</v>
@@ -23243,13 +23353,13 @@
         <v>48</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>2022</v>
+        <v>2031</v>
       </c>
       <c r="Q63" s="0" t="s">
         <v>619</v>
       </c>
       <c r="R63" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S63" s="0" t="s">
         <v>1387</v>
@@ -23263,7 +23373,7 @@
         <v>311</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>2023</v>
+        <v>2032</v>
       </c>
       <c r="C64" s="0" t="s">
         <v>27</v>
@@ -23272,19 +23382,19 @@
         <v>28</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>2024</v>
+        <v>2033</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="H64" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>2026</v>
+        <v>2035</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>303</v>
@@ -23293,10 +23403,10 @@
         <v>57</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>2027</v>
+        <v>2036</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="N64" s="0" t="s">
         <v>70</v>
@@ -23305,16 +23415,16 @@
         <v>48</v>
       </c>
       <c r="P64" s="0" t="s">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="Q64" s="0" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="R64" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S64" s="0" t="s">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="T64" s="0" t="s">
         <v>28</v>
@@ -23322,10 +23432,10 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="C65" s="0" t="s">
         <v>27</v>
@@ -23334,7 +23444,7 @@
         <v>28</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>28</v>
@@ -23346,19 +23456,19 @@
         <v>28</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>2036</v>
+        <v>2045</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>2038</v>
+        <v>2047</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>2039</v>
+        <v>2048</v>
       </c>
       <c r="N65" s="0" t="s">
         <v>28</v>
@@ -23387,7 +23497,7 @@
         <v>1148</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>2040</v>
+        <v>2049</v>
       </c>
       <c r="C66" s="0" t="s">
         <v>27</v>
@@ -23396,28 +23506,28 @@
         <v>28</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>2041</v>
+        <v>2050</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>2042</v>
+        <v>2051</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>2043</v>
+        <v>2052</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>2044</v>
+        <v>2053</v>
       </c>
       <c r="K66" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>2045</v>
+        <v>2054</v>
       </c>
       <c r="M66" s="0" t="s">
         <v>403</v>
@@ -23429,16 +23539,16 @@
         <v>48</v>
       </c>
       <c r="P66" s="0" t="s">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="Q66" s="0" t="s">
-        <v>2047</v>
+        <v>2056</v>
       </c>
       <c r="R66" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S66" s="0" t="s">
-        <v>2048</v>
+        <v>2057</v>
       </c>
       <c r="T66" s="0" t="s">
         <v>28</v>
@@ -23449,7 +23559,7 @@
         <v>41</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>2049</v>
+        <v>2058</v>
       </c>
       <c r="C67" s="0" t="s">
         <v>27</v>
@@ -23458,19 +23568,19 @@
         <v>28</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>2050</v>
+        <v>2059</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>2052</v>
+        <v>2061</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>28</v>
@@ -23479,7 +23589,7 @@
         <v>57</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>2053</v>
+        <v>2062</v>
       </c>
       <c r="M67" s="0" t="s">
         <v>503</v>
@@ -23491,16 +23601,16 @@
         <v>48</v>
       </c>
       <c r="P67" s="0" t="s">
-        <v>2054</v>
+        <v>2063</v>
       </c>
       <c r="Q67" s="0" t="s">
-        <v>2055</v>
+        <v>2064</v>
       </c>
       <c r="R67" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S67" s="0" t="s">
-        <v>2056</v>
+        <v>2065</v>
       </c>
       <c r="T67" s="0" t="s">
         <v>28</v>
@@ -23511,7 +23621,7 @@
         <v>1353</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>2057</v>
+        <v>2066</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>27</v>
@@ -23523,7 +23633,7 @@
         <v>28</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G68" s="0" t="s">
         <v>28</v>
@@ -23532,7 +23642,7 @@
         <v>785</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>2058</v>
+        <v>2067</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>218</v>
@@ -23541,13 +23651,13 @@
         <v>57</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>2059</v>
+        <v>2068</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>2060</v>
+        <v>2069</v>
       </c>
       <c r="N68" s="0" t="s">
-        <v>2061</v>
+        <v>2070</v>
       </c>
       <c r="O68" s="0" t="s">
         <v>48</v>
@@ -23559,7 +23669,7 @@
         <v>1352</v>
       </c>
       <c r="R68" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S68" s="0" t="s">
         <v>1360</v>
@@ -23573,7 +23683,7 @@
         <v>773</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>2062</v>
+        <v>2071</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>27</v>
@@ -23582,31 +23692,31 @@
         <v>28</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>2063</v>
+        <v>2072</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="H69" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>2064</v>
+        <v>2073</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>1986</v>
+        <v>1995</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>1823</v>
+        <v>1832</v>
       </c>
       <c r="N69" s="0" t="s">
         <v>70</v>
@@ -23618,10 +23728,10 @@
         <v>772</v>
       </c>
       <c r="Q69" s="0" t="s">
-        <v>2065</v>
+        <v>2074</v>
       </c>
       <c r="R69" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S69" s="0" t="s">
         <v>227</v>
@@ -23635,7 +23745,7 @@
         <v>781</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>2066</v>
+        <v>2075</v>
       </c>
       <c r="C70" s="0" t="s">
         <v>27</v>
@@ -23644,19 +23754,19 @@
         <v>28</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>2067</v>
+        <v>2076</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>2068</v>
+        <v>2077</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>244</v>
@@ -23665,13 +23775,13 @@
         <v>57</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>2069</v>
+        <v>2078</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>2070</v>
+        <v>2079</v>
       </c>
       <c r="N70" s="0" t="s">
-        <v>2071</v>
+        <v>2080</v>
       </c>
       <c r="O70" s="0" t="s">
         <v>48</v>
@@ -23680,13 +23790,13 @@
         <v>915</v>
       </c>
       <c r="Q70" s="0" t="s">
-        <v>2072</v>
+        <v>2081</v>
       </c>
       <c r="R70" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S70" s="0" t="s">
-        <v>2073</v>
+        <v>2082</v>
       </c>
       <c r="T70" s="0" t="s">
         <v>28</v>
@@ -23694,10 +23804,10 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>2074</v>
+        <v>2083</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>2075</v>
+        <v>2084</v>
       </c>
       <c r="C71" s="0" t="s">
         <v>27</v>
@@ -23706,19 +23816,19 @@
         <v>28</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>2076</v>
+        <v>2085</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="H71" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>2077</v>
+        <v>2086</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>956</v>
@@ -23727,7 +23837,7 @@
         <v>57</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>2078</v>
+        <v>2087</v>
       </c>
       <c r="M71" s="0" t="s">
         <v>1064</v>
@@ -23745,10 +23855,10 @@
         <v>408</v>
       </c>
       <c r="R71" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S71" s="0" t="s">
-        <v>2079</v>
+        <v>2088</v>
       </c>
       <c r="T71" s="0" t="s">
         <v>28</v>
@@ -23756,10 +23866,10 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>2080</v>
+        <v>2089</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>2081</v>
+        <v>2090</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>27</v>
@@ -23768,19 +23878,19 @@
         <v>28</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>2082</v>
+        <v>2091</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="H72" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>2084</v>
+        <v>2093</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>1212</v>
@@ -23789,7 +23899,7 @@
         <v>358</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>2085</v>
+        <v>2094</v>
       </c>
       <c r="M72" s="0" t="s">
         <v>1224</v>
@@ -23801,16 +23911,16 @@
         <v>48</v>
       </c>
       <c r="P72" s="0" t="s">
-        <v>2086</v>
+        <v>2095</v>
       </c>
       <c r="Q72" s="0" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="R72" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S72" s="0" t="s">
-        <v>2088</v>
+        <v>2097</v>
       </c>
       <c r="T72" s="0" t="s">
         <v>28</v>
@@ -23821,7 +23931,7 @@
         <v>197</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>2089</v>
+        <v>2098</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>27</v>
@@ -23833,16 +23943,16 @@
         <v>28</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>2090</v>
+        <v>2099</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>1651</v>
+        <v>1660</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>2091</v>
+        <v>2100</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>303</v>
@@ -23851,13 +23961,13 @@
         <v>57</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>2092</v>
+        <v>2101</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="N73" s="0" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="O73" s="0" t="s">
         <v>48</v>
@@ -23869,7 +23979,7 @@
         <v>266</v>
       </c>
       <c r="R73" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S73" s="0" t="s">
         <v>28</v>
@@ -23883,7 +23993,7 @@
         <v>1292</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>27</v>
@@ -23895,16 +24005,16 @@
         <v>28</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H74" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>2096</v>
+        <v>2105</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>250</v>
@@ -23913,7 +24023,7 @@
         <v>411</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>2097</v>
+        <v>2106</v>
       </c>
       <c r="M74" s="0" t="s">
         <v>376</v>
@@ -23928,10 +24038,10 @@
         <v>371</v>
       </c>
       <c r="Q74" s="0" t="s">
-        <v>2098</v>
+        <v>2107</v>
       </c>
       <c r="R74" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S74" s="0" t="s">
         <v>1296</v>
@@ -23945,7 +24055,7 @@
         <v>454</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>27</v>
@@ -23954,28 +24064,28 @@
         <v>28</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>2100</v>
+        <v>2109</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H75" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>2101</v>
+        <v>2110</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>2102</v>
+        <v>2111</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>2103</v>
+        <v>2112</v>
       </c>
       <c r="M75" s="0" t="s">
         <v>531</v>
@@ -23990,13 +24100,13 @@
         <v>845</v>
       </c>
       <c r="Q75" s="0" t="s">
-        <v>2104</v>
+        <v>2113</v>
       </c>
       <c r="R75" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>2105</v>
+        <v>2114</v>
       </c>
       <c r="T75" s="0" t="s">
         <v>28</v>
@@ -24007,7 +24117,7 @@
         <v>464</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>2106</v>
+        <v>2115</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>27</v>
@@ -24019,25 +24129,25 @@
         <v>542</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>2107</v>
+        <v>2116</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>2108</v>
+        <v>2117</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>2109</v>
+        <v>2118</v>
       </c>
       <c r="M76" s="0" t="s">
         <v>440</v>
@@ -24049,13 +24159,13 @@
         <v>48</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>2110</v>
+        <v>2119</v>
       </c>
       <c r="Q76" s="0" t="s">
         <v>462</v>
       </c>
       <c r="R76" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S76" s="0" t="s">
         <v>466</v>
@@ -24066,10 +24176,10 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>2111</v>
+        <v>2120</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>2112</v>
+        <v>2121</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>27</v>
@@ -24081,16 +24191,16 @@
         <v>28</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>2113</v>
+        <v>2122</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>828</v>
@@ -24099,7 +24209,7 @@
         <v>57</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>2114</v>
+        <v>2123</v>
       </c>
       <c r="M77" s="0" t="s">
         <v>457</v>
@@ -24114,13 +24224,13 @@
         <v>310</v>
       </c>
       <c r="Q77" s="0" t="s">
-        <v>2115</v>
+        <v>2124</v>
       </c>
       <c r="R77" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S77" s="0" t="s">
-        <v>2116</v>
+        <v>2125</v>
       </c>
       <c r="T77" s="0" t="s">
         <v>28</v>
@@ -24131,7 +24241,7 @@
         <v>1501</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>2117</v>
+        <v>2126</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>27</v>
@@ -24143,16 +24253,16 @@
         <v>28</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="H78" s="0" t="s">
         <v>28</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>2118</v>
+        <v>2127</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>426</v>
@@ -24161,25 +24271,25 @@
         <v>57</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>2120</v>
+        <v>2129</v>
       </c>
       <c r="N78" s="0" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="O78" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
       <c r="Q78" s="0" t="s">
-        <v>2123</v>
+        <v>2132</v>
       </c>
       <c r="R78" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S78" s="0" t="s">
         <v>1503</v>
@@ -24190,10 +24300,10 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2124</v>
+        <v>2133</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>2125</v>
+        <v>2134</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>27</v>
@@ -24205,16 +24315,16 @@
         <v>28</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>2090</v>
+        <v>2099</v>
       </c>
       <c r="H79" s="0" t="s">
         <v>995</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>2126</v>
+        <v>2135</v>
       </c>
       <c r="J79" s="0" t="s">
         <v>543</v>
@@ -24235,13 +24345,13 @@
         <v>48</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>2127</v>
+        <v>2136</v>
       </c>
       <c r="Q79" s="0" t="s">
         <v>991</v>
       </c>
       <c r="R79" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S79" s="0" t="s">
         <v>996</v>
@@ -24252,10 +24362,10 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>2128</v>
+        <v>2137</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>2129</v>
+        <v>2138</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>27</v>
@@ -24264,19 +24374,19 @@
         <v>28</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>2130</v>
+        <v>2139</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>2131</v>
+        <v>2140</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>2132</v>
+        <v>2141</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>2091</v>
+        <v>2100</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>303</v>
@@ -24285,13 +24395,13 @@
         <v>57</v>
       </c>
       <c r="L80" s="0" t="s">
-        <v>2092</v>
+        <v>2101</v>
       </c>
       <c r="M80" s="0" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="N80" s="0" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="O80" s="0" t="s">
         <v>48</v>
@@ -24303,10 +24413,10 @@
         <v>266</v>
       </c>
       <c r="R80" s="0" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="S80" s="0" t="s">
-        <v>2133</v>
+        <v>2142</v>
       </c>
       <c r="T80" s="0" t="s">
         <v>28</v>
@@ -24314,10 +24424,10 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>2134</v>
+        <v>2143</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>2135</v>
+        <v>2144</v>
       </c>
       <c r="C81" s="0" t="s">
         <v>27</v>
@@ -24329,25 +24439,25 @@
         <v>28</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>2136</v>
+        <v>2145</v>
       </c>
       <c r="H81" s="0" t="s">
         <v>70</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>2137</v>
+        <v>2146</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>1641</v>
+        <v>1650</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>2138</v>
+        <v>2147</v>
       </c>
       <c r="M81" s="0" t="s">
         <v>69</v>
@@ -24356,21 +24466,83 @@
         <v>70</v>
       </c>
       <c r="O81" s="0" t="s">
-        <v>2139</v>
+        <v>1518</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>2140</v>
+        <v>2148</v>
       </c>
       <c r="Q81" s="0" t="s">
-        <v>2141</v>
+        <v>2149</v>
       </c>
       <c r="R81" s="0" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="S81" s="0" t="s">
         <v>28</v>
       </c>
       <c r="T81" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>2152</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="I82" s="0" t="s">
+        <v>2153</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>909</v>
+      </c>
+      <c r="K82" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" s="0" t="s">
+        <v>2154</v>
+      </c>
+      <c r="M82" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="N82" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>1518</v>
+      </c>
+      <c r="P82" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q82" s="0" t="s">
+        <v>1512</v>
+      </c>
+      <c r="R82" s="0" t="s">
+        <v>1975</v>
+      </c>
+      <c r="S82" s="0" t="s">
+        <v>2155</v>
+      </c>
+      <c r="T82" s="0" t="s">
         <v>28</v>
       </c>
     </row>

--- a/Data/BDD_IQS_Person.xlsx
+++ b/Data/BDD_IQS_Person.xlsx
@@ -6,15 +6,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1005" yWindow="-120" windowWidth="27915" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="33" d3p1:id="rId35"/>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="34" d3p1:id="rId36"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="37" d3p1:id="rId39"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="38" d3p1:id="rId40"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="2192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="2193">
   <si>
     <t>Id</t>
   </si>
@@ -6413,6 +6413,9 @@
   </si>
   <si>
     <t>TH Records</t>
+  </si>
+  <si>
+    <t>1222153016</t>
   </si>
   <si>
     <t>921 728 556</t>
@@ -6907,7 +6910,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:V189"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19769,7 +19772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:T83"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24311,7 +24314,7 @@
         <v>28</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>28</v>
+        <v>2133</v>
       </c>
       <c r="E74" s="0" t="s">
         <v>1556</v>
@@ -24323,7 +24326,7 @@
         <v>70</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="I74" s="0" t="s">
         <v>29</v>
@@ -24335,7 +24338,7 @@
         <v>410</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="M74" s="0" t="s">
         <v>375</v>
@@ -24350,7 +24353,7 @@
         <v>370</v>
       </c>
       <c r="Q74" s="0" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="R74" s="0" t="s">
         <v>1560</v>
@@ -24367,13 +24370,13 @@
         <v>454</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="E75" s="0" t="s">
         <v>1556</v>
@@ -24385,19 +24388,19 @@
         <v>992</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="I75" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="M75" s="0" t="s">
         <v>529</v>
@@ -24412,13 +24415,13 @@
         <v>842</v>
       </c>
       <c r="Q75" s="0" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="R75" s="0" t="s">
         <v>1560</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="T75" s="0" t="s">
         <v>28</v>
@@ -24429,7 +24432,7 @@
         <v>464</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>28</v>
@@ -24447,19 +24450,19 @@
         <v>70</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="M76" s="0" t="s">
         <v>439</v>
@@ -24471,7 +24474,7 @@
         <v>48</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Q76" s="0" t="s">
         <v>461</v>
@@ -24488,10 +24491,10 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>28</v>
@@ -24509,7 +24512,7 @@
         <v>70</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="I77" s="0" t="s">
         <v>29</v>
@@ -24521,7 +24524,7 @@
         <v>57</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="M77" s="0" t="s">
         <v>456</v>
@@ -24536,13 +24539,13 @@
         <v>310</v>
       </c>
       <c r="Q77" s="0" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="R77" s="0" t="s">
         <v>1560</v>
       </c>
       <c r="S77" s="0" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="T77" s="0" t="s">
         <v>28</v>
@@ -24553,7 +24556,7 @@
         <v>1498</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>28</v>
@@ -24571,7 +24574,7 @@
         <v>28</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>29</v>
@@ -24583,22 +24586,22 @@
         <v>57</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="N78" s="0" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="O78" s="0" t="s">
         <v>48</v>
       </c>
       <c r="P78" s="0" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="Q78" s="0" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="R78" s="0" t="s">
         <v>1570</v>
@@ -24612,10 +24615,10 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>28</v>
@@ -24633,7 +24636,7 @@
         <v>992</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>29</v>
@@ -24657,7 +24660,7 @@
         <v>48</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="Q79" s="0" t="s">
         <v>988</v>
@@ -24674,25 +24677,25 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>1768</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>2127</v>
@@ -24728,7 +24731,7 @@
         <v>1570</v>
       </c>
       <c r="S80" s="0" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="T80" s="0" t="s">
         <v>28</v>
@@ -24736,10 +24739,10 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="C81" s="0" t="s">
         <v>28</v>
@@ -24751,13 +24754,13 @@
         <v>1556</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="I81" s="0" t="s">
         <v>29</v>
@@ -24769,7 +24772,7 @@
         <v>57</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="M81" s="0" t="s">
         <v>69</v>
@@ -24781,16 +24784,16 @@
         <v>1514</v>
       </c>
       <c r="P81" s="0" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="Q81" s="0" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="R81" s="0" t="s">
         <v>1560</v>
       </c>
       <c r="S81" s="0" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="T81" s="0" t="s">
         <v>28</v>
@@ -24798,10 +24801,10 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C82" s="0" t="s">
         <v>28</v>
@@ -24813,13 +24816,13 @@
         <v>1556</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>29</v>
@@ -24831,7 +24834,7 @@
         <v>57</v>
       </c>
       <c r="L82" s="0" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="M82" s="0" t="s">
         <v>1859</v>
@@ -24860,10 +24863,10 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>28</v>
@@ -24881,7 +24884,7 @@
         <v>1011</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>29</v>
@@ -24893,7 +24896,7 @@
         <v>57</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="M83" s="0" t="s">
         <v>1010</v>
@@ -24905,19 +24908,19 @@
         <v>1514</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="Q83" s="0" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="R83" s="0" t="s">
         <v>1560</v>
       </c>
       <c r="S83" s="0" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="T83" s="0" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
   </sheetData>

--- a/Data/BDD_IQS_Person.xlsx
+++ b/Data/BDD_IQS_Person.xlsx
@@ -6,15 +6,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1005" yWindow="-120" windowWidth="27915" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="37" d3p1:id="rId39"/>
-    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="38" d3p1:id="rId40"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEPHYSIQUE" sheetId="43" d3p1:id="rId45"/>
+    <sheet xmlns:d3p1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSONNEMORALE" sheetId="44" d3p1:id="rId46"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="2193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="2194">
   <si>
     <t>Id</t>
   </si>
@@ -4582,18 +4582,12 @@
     <t>00111189881</t>
   </si>
   <si>
-    <t>SADAIC</t>
-  </si>
-  <si>
-    <t>M00082:100</t>
+    <t>M00083:100</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>rue</t>
-  </si>
-  <si>
     <t>Gaston</t>
   </si>
   <si>
@@ -6538,6 +6532,9 @@
     <t>LONGUE VIE PUBLISHING</t>
   </si>
   <si>
+    <t>1314677451</t>
+  </si>
+  <si>
     <t>100 €</t>
   </si>
   <si>
@@ -6562,6 +6559,9 @@
     <t>LE PACTE PUBLISHING</t>
   </si>
   <si>
+    <t>1314677549</t>
+  </si>
+  <si>
     <t>1000 €</t>
   </si>
   <si>
@@ -6575,6 +6575,9 @@
   </si>
   <si>
     <t>JOUUUE PUBLISHING</t>
+  </si>
+  <si>
+    <t>383996498</t>
   </si>
   <si>
     <t>849668256</t>
@@ -6910,7 +6913,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:V189"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19592,31 +19595,31 @@
         <v>28</v>
       </c>
       <c r="J187" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="K187" s="0" t="s">
         <v>1522</v>
       </c>
-      <c r="K187" s="0" t="s">
+      <c r="L187" s="0" t="s">
         <v>1523</v>
       </c>
-      <c r="L187" s="0" t="s">
+      <c r="M187" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="N187" s="0" t="s">
         <v>1524</v>
       </c>
-      <c r="M187" s="0" t="s">
+      <c r="O187" s="0" t="s">
         <v>1525</v>
       </c>
-      <c r="N187" s="0" t="s">
+      <c r="P187" s="0" t="s">
         <v>1526</v>
-      </c>
-      <c r="O187" s="0" t="s">
-        <v>1527</v>
-      </c>
-      <c r="P187" s="0" t="s">
-        <v>1528</v>
       </c>
       <c r="Q187" s="0" t="s">
         <v>1514</v>
       </c>
       <c r="R187" s="0" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="S187" s="0" t="s">
         <v>28</v>
@@ -19633,16 +19636,16 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B188" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C188" s="0" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D188" s="0" t="s">
         <v>1530</v>
-      </c>
-      <c r="B188" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C188" s="0" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D188" s="0" t="s">
-        <v>1532</v>
       </c>
       <c r="E188" s="0" t="s">
         <v>1520</v>
@@ -19654,7 +19657,7 @@
         <v>28</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>28</v>
@@ -19678,13 +19681,13 @@
         <v>151</v>
       </c>
       <c r="P188" s="0" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="Q188" s="0" t="s">
         <v>48</v>
       </c>
       <c r="R188" s="0" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="S188" s="0" t="s">
         <v>28</v>
@@ -19701,16 +19704,16 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B189" s="0" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C189" s="0" t="s">
         <v>1536</v>
       </c>
-      <c r="B189" s="0" t="s">
+      <c r="D189" s="0" t="s">
         <v>1537</v>
-      </c>
-      <c r="C189" s="0" t="s">
-        <v>1538</v>
-      </c>
-      <c r="D189" s="0" t="s">
-        <v>1539</v>
       </c>
       <c r="E189" s="0" t="s">
         <v>1520</v>
@@ -19731,28 +19734,28 @@
         <v>29</v>
       </c>
       <c r="K189" s="0" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L189" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="M189" s="0" t="s">
+        <v>1539</v>
+      </c>
+      <c r="N189" s="0" t="s">
         <v>1540</v>
       </c>
-      <c r="L189" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="M189" s="0" t="s">
+      <c r="O189" s="0" t="s">
         <v>1541</v>
       </c>
-      <c r="N189" s="0" t="s">
+      <c r="P189" s="0" t="s">
         <v>1542</v>
-      </c>
-      <c r="O189" s="0" t="s">
-        <v>1543</v>
-      </c>
-      <c r="P189" s="0" t="s">
-        <v>1544</v>
       </c>
       <c r="Q189" s="0" t="s">
         <v>1514</v>
       </c>
       <c r="R189" s="0" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="S189" s="0" t="s">
         <v>28</v>
@@ -19772,7 +19775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:T83"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19782,7 +19785,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
@@ -19791,16 +19794,16 @@
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1547</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1548</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1549</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1550</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>9</v>
@@ -19824,13 +19827,13 @@
         <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>1551</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>1553</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>17</v>
@@ -19844,25 +19847,25 @@
         <v>619</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>1554</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>1555</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>1557</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="I2" s="0" t="s">
         <v>29</v>
@@ -19886,13 +19889,13 @@
         <v>48</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="Q2" s="0" t="s">
         <v>516</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>621</v>
@@ -19903,40 +19906,40 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>1561</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="D3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>1562</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>1564</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K3" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>1060</v>
@@ -19948,16 +19951,16 @@
         <v>48</v>
       </c>
       <c r="P3" s="0" t="s">
+        <v>1566</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>1567</v>
+      </c>
+      <c r="R3" s="0" t="s">
         <v>1568</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="S3" s="0" t="s">
         <v>1569</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S3" s="0" t="s">
-        <v>1571</v>
       </c>
       <c r="T3" s="0" t="s">
         <v>28</v>
@@ -19965,28 +19968,28 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>1572</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="E4" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>1573</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>1574</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>1575</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>29</v>
@@ -19998,7 +20001,7 @@
         <v>57</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>69</v>
@@ -20013,13 +20016,13 @@
         <v>1106</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="T4" s="0" t="s">
         <v>28</v>
@@ -20027,90 +20030,90 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>1580</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="E5" s="0" t="s">
         <v>1581</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="F5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="0" t="s">
         <v>1582</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="I5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="0" t="s">
         <v>1583</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="0" t="s">
+      <c r="K5" s="0" t="s">
         <v>1584</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="0" t="s">
+      <c r="L5" s="0" t="s">
         <v>1585</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="M5" s="0" t="s">
         <v>1586</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="N5" s="0" t="s">
         <v>1587</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="O5" s="0" t="s">
         <v>1588</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="P5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="R5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S5" s="0" t="s">
         <v>1589</v>
       </c>
-      <c r="O5" s="0" t="s">
+      <c r="T5" s="0" t="s">
         <v>1590</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="R5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" s="0" t="s">
-        <v>1591</v>
-      </c>
-      <c r="T5" s="0" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>1593</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="E6" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>1594</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>1595</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>1596</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>29</v>
@@ -20122,7 +20125,7 @@
         <v>57</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>163</v>
@@ -20134,16 +20137,16 @@
         <v>48</v>
       </c>
       <c r="P6" s="0" t="s">
+        <v>1597</v>
+      </c>
+      <c r="Q6" s="0" t="s">
+        <v>1598</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S6" s="0" t="s">
         <v>1599</v>
-      </c>
-      <c r="Q6" s="0" t="s">
-        <v>1600</v>
-      </c>
-      <c r="R6" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>1601</v>
       </c>
       <c r="T6" s="0" t="s">
         <v>28</v>
@@ -20151,40 +20154,40 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="0" t="s">
         <v>1602</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="E7" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>1603</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>1605</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I7" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>447</v>
@@ -20196,16 +20199,16 @@
         <v>48</v>
       </c>
       <c r="P7" s="0" t="s">
+        <v>1607</v>
+      </c>
+      <c r="Q7" s="0" t="s">
+        <v>1608</v>
+      </c>
+      <c r="R7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="0" t="s">
         <v>1609</v>
-      </c>
-      <c r="Q7" s="0" t="s">
-        <v>1610</v>
-      </c>
-      <c r="R7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="S7" s="0" t="s">
-        <v>1611</v>
       </c>
       <c r="T7" s="0" t="s">
         <v>28</v>
@@ -20216,25 +20219,25 @@
         <v>1125</v>
       </c>
       <c r="B8" s="0" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>1612</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="F8" s="0" t="s">
         <v>1613</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>1615</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I8" s="0" t="s">
         <v>29</v>
@@ -20246,7 +20249,7 @@
         <v>312</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>349</v>
@@ -20261,16 +20264,16 @@
         <v>1183</v>
       </c>
       <c r="Q8" s="0" t="s">
+        <v>1616</v>
+      </c>
+      <c r="R8" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S8" s="0" t="s">
+        <v>1617</v>
+      </c>
+      <c r="T8" s="0" t="s">
         <v>1618</v>
-      </c>
-      <c r="R8" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S8" s="0" t="s">
-        <v>1619</v>
-      </c>
-      <c r="T8" s="0" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="9">
@@ -20278,31 +20281,31 @@
         <v>932</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>1621</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="F9" s="0" t="s">
         <v>1622</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>1624</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="K9" s="0" t="s">
         <v>57</v>
@@ -20311,25 +20314,25 @@
         <v>392</v>
       </c>
       <c r="M9" s="0" t="s">
+        <v>1625</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>1626</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="0" t="s">
         <v>1627</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="Q9" s="0" t="s">
         <v>1628</v>
       </c>
-      <c r="O9" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="0" t="s">
+      <c r="R9" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S9" s="0" t="s">
         <v>1629</v>
-      </c>
-      <c r="Q9" s="0" t="s">
-        <v>1630</v>
-      </c>
-      <c r="R9" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S9" s="0" t="s">
-        <v>1631</v>
       </c>
       <c r="T9" s="0" t="s">
         <v>28</v>
@@ -20337,28 +20340,28 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F10" s="0" t="s">
         <v>1632</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>1634</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>29</v>
@@ -20370,57 +20373,57 @@
         <v>57</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>1075</v>
       </c>
       <c r="N10" s="0" t="s">
+        <v>1635</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>1636</v>
+      </c>
+      <c r="Q10" s="0" t="s">
         <v>1637</v>
       </c>
-      <c r="O10" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P10" s="0" t="s">
+      <c r="R10" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S10" s="0" t="s">
         <v>1638</v>
       </c>
-      <c r="Q10" s="0" t="s">
+      <c r="T10" s="0" t="s">
         <v>1639</v>
-      </c>
-      <c r="R10" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S10" s="0" t="s">
-        <v>1640</v>
-      </c>
-      <c r="T10" s="0" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>1642</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="F11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="0" t="s">
         <v>1643</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>1645</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>29</v>
@@ -20432,7 +20435,7 @@
         <v>57</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>908</v>
@@ -20453,7 +20456,7 @@
         <v>28</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="T11" s="0" t="s">
         <v>28</v>
@@ -20464,25 +20467,25 @@
         <v>446</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>29</v>
@@ -20491,28 +20494,28 @@
         <v>425</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>654</v>
       </c>
       <c r="N12" s="0" t="s">
+        <v>1651</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12" s="0" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Q12" s="0" t="s">
         <v>1653</v>
       </c>
-      <c r="O12" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="0" t="s">
-        <v>1654</v>
-      </c>
-      <c r="Q12" s="0" t="s">
-        <v>1655</v>
-      </c>
       <c r="R12" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S12" s="0" t="s">
         <v>448</v>
@@ -20523,40 +20526,40 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="0" t="s">
         <v>1656</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="I13" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="0" t="s">
         <v>1657</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>1658</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>1659</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>908</v>
@@ -20568,16 +20571,16 @@
         <v>48</v>
       </c>
       <c r="P13" s="0" t="s">
+        <v>1659</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>1660</v>
+      </c>
+      <c r="R13" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S13" s="0" t="s">
         <v>1661</v>
-      </c>
-      <c r="Q13" s="0" t="s">
-        <v>1662</v>
-      </c>
-      <c r="R13" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S13" s="0" t="s">
-        <v>1663</v>
       </c>
       <c r="T13" s="0" t="s">
         <v>28</v>
@@ -20585,10 +20588,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>28</v>
@@ -20597,7 +20600,7 @@
         <v>28</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F14" s="0" t="s">
         <v>28</v>
@@ -20606,40 +20609,40 @@
         <v>1037</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="I14" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L14" s="0" t="s">
+        <v>1666</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>1667</v>
+      </c>
+      <c r="N14" s="0" t="s">
         <v>1668</v>
       </c>
-      <c r="M14" s="0" t="s">
+      <c r="O14" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" s="0" t="s">
         <v>1669</v>
       </c>
-      <c r="N14" s="0" t="s">
+      <c r="Q14" s="0" t="s">
         <v>1670</v>
       </c>
-      <c r="O14" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P14" s="0" t="s">
+      <c r="R14" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S14" s="0" t="s">
         <v>1671</v>
-      </c>
-      <c r="Q14" s="0" t="s">
-        <v>1672</v>
-      </c>
-      <c r="R14" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S14" s="0" t="s">
-        <v>1673</v>
       </c>
       <c r="T14" s="0" t="s">
         <v>28</v>
@@ -20647,10 +20650,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>28</v>
@@ -20659,49 +20662,49 @@
         <v>28</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>560</v>
       </c>
       <c r="H15" s="0" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>1649</v>
+      </c>
+      <c r="L15" s="0" t="s">
         <v>1676</v>
       </c>
-      <c r="I15" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="0" t="s">
+      <c r="M15" s="0" t="s">
         <v>1677</v>
       </c>
-      <c r="K15" s="0" t="s">
-        <v>1651</v>
-      </c>
-      <c r="L15" s="0" t="s">
+      <c r="N15" s="0" t="s">
         <v>1678</v>
       </c>
-      <c r="M15" s="0" t="s">
+      <c r="O15" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P15" s="0" t="s">
         <v>1679</v>
       </c>
-      <c r="N15" s="0" t="s">
+      <c r="Q15" s="0" t="s">
         <v>1680</v>
       </c>
-      <c r="O15" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P15" s="0" t="s">
+      <c r="R15" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S15" s="0" t="s">
         <v>1681</v>
-      </c>
-      <c r="Q15" s="0" t="s">
-        <v>1682</v>
-      </c>
-      <c r="R15" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S15" s="0" t="s">
-        <v>1683</v>
       </c>
       <c r="T15" s="0" t="s">
         <v>28</v>
@@ -20709,28 +20712,28 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>1684</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="E16" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G16" s="0" t="s">
         <v>1685</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="H16" s="0" t="s">
         <v>1686</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>1624</v>
-      </c>
-      <c r="G16" s="0" t="s">
-        <v>1687</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>1688</v>
       </c>
       <c r="I16" s="0" t="s">
         <v>29</v>
@@ -20739,28 +20742,28 @@
         <v>30</v>
       </c>
       <c r="K16" s="0" t="s">
+        <v>1687</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>1688</v>
+      </c>
+      <c r="M16" s="0" t="s">
         <v>1689</v>
       </c>
-      <c r="L16" s="0" t="s">
+      <c r="N16" s="0" t="s">
         <v>1690</v>
       </c>
-      <c r="M16" s="0" t="s">
+      <c r="O16" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P16" s="0" t="s">
         <v>1691</v>
       </c>
-      <c r="N16" s="0" t="s">
+      <c r="Q16" s="0" t="s">
         <v>1692</v>
       </c>
-      <c r="O16" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="0" t="s">
-        <v>1693</v>
-      </c>
-      <c r="Q16" s="0" t="s">
-        <v>1694</v>
-      </c>
       <c r="R16" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S16" s="0" t="s">
         <v>28</v>
@@ -20774,25 +20777,25 @@
         <v>1452</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>1450</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="I17" s="0" t="s">
         <v>29</v>
@@ -20807,10 +20810,10 @@
         <v>1245</v>
       </c>
       <c r="M17" s="0" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="O17" s="0" t="s">
         <v>48</v>
@@ -20819,7 +20822,7 @@
         <v>1449</v>
       </c>
       <c r="Q17" s="0" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="R17" s="0" t="s">
         <v>28</v>
@@ -20833,28 +20836,28 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="0" t="s">
         <v>1701</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>1702</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>1703</v>
-      </c>
       <c r="E18" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>29</v>
@@ -20866,7 +20869,7 @@
         <v>57</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="M18" s="0" t="s">
         <v>447</v>
@@ -20881,13 +20884,13 @@
         <v>564</v>
       </c>
       <c r="Q18" s="0" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="R18" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="T18" s="0" t="s">
         <v>28</v>
@@ -20898,25 +20901,25 @@
         <v>815</v>
       </c>
       <c r="B19" s="0" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H19" s="0" t="s">
         <v>1708</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>1624</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>1709</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>1710</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>29</v>
@@ -20928,28 +20931,28 @@
         <v>410</v>
       </c>
       <c r="L19" s="0" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>1710</v>
+      </c>
+      <c r="N19" s="0" t="s">
         <v>1711</v>
       </c>
-      <c r="M19" s="0" t="s">
+      <c r="O19" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P19" s="0" t="s">
         <v>1712</v>
       </c>
-      <c r="N19" s="0" t="s">
+      <c r="Q19" s="0" t="s">
         <v>1713</v>
       </c>
-      <c r="O19" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P19" s="0" t="s">
+      <c r="R19" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S19" s="0" t="s">
         <v>1714</v>
-      </c>
-      <c r="Q19" s="0" t="s">
-        <v>1715</v>
-      </c>
-      <c r="R19" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S19" s="0" t="s">
-        <v>1716</v>
       </c>
       <c r="T19" s="0" t="s">
         <v>28</v>
@@ -20957,28 +20960,28 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F20" s="0" t="s">
         <v>1717</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="G20" s="0" t="s">
         <v>1718</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F20" s="0" t="s">
+      <c r="H20" s="0" t="s">
         <v>1719</v>
-      </c>
-      <c r="G20" s="0" t="s">
-        <v>1720</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>1721</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>29</v>
@@ -20993,45 +20996,45 @@
         <v>219</v>
       </c>
       <c r="M20" s="0" t="s">
+        <v>1720</v>
+      </c>
+      <c r="N20" s="0" t="s">
+        <v>1721</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P20" s="0" t="s">
         <v>1722</v>
       </c>
-      <c r="N20" s="0" t="s">
+      <c r="Q20" s="0" t="s">
         <v>1723</v>
       </c>
-      <c r="O20" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P20" s="0" t="s">
+      <c r="R20" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S20" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="T20" s="0" t="s">
         <v>1724</v>
-      </c>
-      <c r="Q20" s="0" t="s">
-        <v>1725</v>
-      </c>
-      <c r="R20" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S20" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="T20" s="0" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="0" t="s">
         <v>1727</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>1728</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>1729</v>
-      </c>
       <c r="E21" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>28</v>
@@ -21052,7 +21055,7 @@
         <v>57</v>
       </c>
       <c r="L21" s="0" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="M21" s="0" t="s">
         <v>172</v>
@@ -21070,7 +21073,7 @@
         <v>28</v>
       </c>
       <c r="R21" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S21" s="0" t="s">
         <v>1420</v>
@@ -21084,37 +21087,37 @@
         <v>342</v>
       </c>
       <c r="B22" s="0" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F22" s="0" t="s">
         <v>1731</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>1732</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F22" s="0" t="s">
-        <v>1733</v>
       </c>
       <c r="G22" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="K22" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L22" s="0" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="M22" s="0" t="s">
         <v>337</v>
@@ -21132,7 +21135,7 @@
         <v>341</v>
       </c>
       <c r="R22" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S22" s="0" t="s">
         <v>343</v>
@@ -21146,43 +21149,43 @@
         <v>273</v>
       </c>
       <c r="B23" s="0" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G23" s="0" t="s">
         <v>1737</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="H23" s="0" t="s">
         <v>1738</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>1634</v>
-      </c>
-      <c r="G23" s="0" t="s">
+      <c r="I23" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" s="0" t="s">
         <v>1739</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="L23" s="0" t="s">
         <v>1740</v>
       </c>
-      <c r="I23" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="0" t="s">
+      <c r="M23" s="0" t="s">
         <v>1741</v>
       </c>
-      <c r="L23" s="0" t="s">
+      <c r="N23" s="0" t="s">
         <v>1742</v>
-      </c>
-      <c r="M23" s="0" t="s">
-        <v>1743</v>
-      </c>
-      <c r="N23" s="0" t="s">
-        <v>1744</v>
       </c>
       <c r="O23" s="0" t="s">
         <v>48</v>
@@ -21191,13 +21194,13 @@
         <v>380</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="R23" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="T23" s="0" t="s">
         <v>28</v>
@@ -21208,58 +21211,58 @@
         <v>87</v>
       </c>
       <c r="B24" s="0" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D24" s="0" t="s">
         <v>1747</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="E24" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="0" t="s">
         <v>1748</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="H24" s="0" t="s">
         <v>1749</v>
       </c>
-      <c r="E24" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="0" t="s">
+      <c r="I24" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="0" t="s">
         <v>1750</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>1751</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>1752</v>
       </c>
       <c r="K24" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L24" s="0" t="s">
+        <v>1751</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>1752</v>
+      </c>
+      <c r="N24" s="0" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="0" t="s">
         <v>1753</v>
       </c>
-      <c r="M24" s="0" t="s">
+      <c r="Q24" s="0" t="s">
         <v>1754</v>
       </c>
-      <c r="N24" s="0" t="s">
-        <v>1750</v>
-      </c>
-      <c r="O24" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="0" t="s">
+      <c r="R24" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S24" s="0" t="s">
         <v>1755</v>
-      </c>
-      <c r="Q24" s="0" t="s">
-        <v>1756</v>
-      </c>
-      <c r="R24" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S24" s="0" t="s">
-        <v>1757</v>
       </c>
       <c r="T24" s="0" t="s">
         <v>28</v>
@@ -21267,40 +21270,40 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C25" s="0" t="s">
         <v>1758</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="D25" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F25" s="0" t="s">
         <v>1759</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>1761</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K25" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M25" s="0" t="s">
         <v>1060</v>
@@ -21312,16 +21315,16 @@
         <v>48</v>
       </c>
       <c r="P25" s="0" t="s">
+        <v>1761</v>
+      </c>
+      <c r="Q25" s="0" t="s">
+        <v>1762</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S25" s="0" t="s">
         <v>1763</v>
-      </c>
-      <c r="Q25" s="0" t="s">
-        <v>1764</v>
-      </c>
-      <c r="R25" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S25" s="0" t="s">
-        <v>1765</v>
       </c>
       <c r="T25" s="0" t="s">
         <v>28</v>
@@ -21332,37 +21335,37 @@
         <v>372</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E26" s="0" t="s">
         <v>1766</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>1767</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>1768</v>
-      </c>
       <c r="F26" s="0" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G26" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="I26" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="K26" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="M26" s="0" t="s">
         <v>447</v>
@@ -21380,7 +21383,7 @@
         <v>369</v>
       </c>
       <c r="R26" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S26" s="0" t="s">
         <v>376</v>
@@ -21394,7 +21397,7 @@
         <v>208</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>28</v>
@@ -21424,16 +21427,16 @@
         <v>28</v>
       </c>
       <c r="L27" s="0" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="M27" s="0" t="s">
         <v>211</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="P27" s="0" t="s">
         <v>206</v>
@@ -21442,7 +21445,7 @@
         <v>205</v>
       </c>
       <c r="R27" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S27" s="0" t="s">
         <v>213</v>
@@ -21456,16 +21459,16 @@
         <v>1407</v>
       </c>
       <c r="B28" s="0" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E28" s="0" t="s">
         <v>1776</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>1777</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>1778</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>28</v>
@@ -21474,7 +21477,7 @@
         <v>992</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>29</v>
@@ -21504,7 +21507,7 @@
         <v>1404</v>
       </c>
       <c r="R28" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S28" s="0" t="s">
         <v>1411</v>
@@ -21515,28 +21518,28 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="0" t="s">
         <v>1780</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="E29" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G29" s="0" t="s">
         <v>1781</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="H29" s="0" t="s">
         <v>1782</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G29" s="0" t="s">
-        <v>1783</v>
-      </c>
-      <c r="H29" s="0" t="s">
-        <v>1784</v>
       </c>
       <c r="I29" s="0" t="s">
         <v>29</v>
@@ -21548,13 +21551,13 @@
         <v>357</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="M29" s="0" t="s">
         <v>898</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="O29" s="0" t="s">
         <v>48</v>
@@ -21563,13 +21566,13 @@
         <v>310</v>
       </c>
       <c r="Q29" s="0" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="R29" s="0" t="s">
         <v>28</v>
       </c>
       <c r="S29" s="0" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="T29" s="0" t="s">
         <v>28</v>
@@ -21580,25 +21583,25 @@
         <v>471</v>
       </c>
       <c r="B30" s="0" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F30" s="0" t="s">
         <v>1789</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>1790</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>1791</v>
       </c>
       <c r="G30" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="I30" s="0" t="s">
         <v>29</v>
@@ -21610,7 +21613,7 @@
         <v>123</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="M30" s="0" t="s">
         <v>439</v>
@@ -21622,13 +21625,13 @@
         <v>48</v>
       </c>
       <c r="P30" s="0" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="Q30" s="0" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="R30" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S30" s="0" t="s">
         <v>28</v>
@@ -21639,28 +21642,28 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="0" t="s">
         <v>1796</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="E31" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F31" s="0" t="s">
         <v>1797</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>1798</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>1799</v>
       </c>
       <c r="G31" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>29</v>
@@ -21672,7 +21675,7 @@
         <v>57</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="M31" s="0" t="s">
         <v>1399</v>
@@ -21684,45 +21687,45 @@
         <v>48</v>
       </c>
       <c r="P31" s="0" t="s">
+        <v>1800</v>
+      </c>
+      <c r="Q31" s="0" t="s">
+        <v>1801</v>
+      </c>
+      <c r="R31" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S31" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="T31" s="0" t="s">
         <v>1802</v>
-      </c>
-      <c r="Q31" s="0" t="s">
-        <v>1803</v>
-      </c>
-      <c r="R31" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S31" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="T31" s="0" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="0" t="s">
         <v>1805</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="E32" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F32" s="0" t="s">
         <v>1806</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>1807</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>1808</v>
       </c>
       <c r="G32" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>29</v>
@@ -21734,10 +21737,10 @@
         <v>57</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="N32" s="0" t="s">
         <v>70</v>
@@ -21746,16 +21749,16 @@
         <v>48</v>
       </c>
       <c r="P32" s="0" t="s">
+        <v>1810</v>
+      </c>
+      <c r="Q32" s="0" t="s">
+        <v>1811</v>
+      </c>
+      <c r="R32" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S32" s="0" t="s">
         <v>1812</v>
-      </c>
-      <c r="Q32" s="0" t="s">
-        <v>1813</v>
-      </c>
-      <c r="R32" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S32" s="0" t="s">
-        <v>1814</v>
       </c>
       <c r="T32" s="0" t="s">
         <v>28</v>
@@ -21766,25 +21769,25 @@
         <v>121</v>
       </c>
       <c r="B33" s="0" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>1814</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F33" s="0" t="s">
         <v>1815</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>1816</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>1817</v>
       </c>
       <c r="G33" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>29</v>
@@ -21796,7 +21799,7 @@
         <v>57</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="M33" s="0" t="s">
         <v>1220</v>
@@ -21808,16 +21811,16 @@
         <v>48</v>
       </c>
       <c r="P33" s="0" t="s">
+        <v>1818</v>
+      </c>
+      <c r="Q33" s="0" t="s">
+        <v>1819</v>
+      </c>
+      <c r="R33" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S33" s="0" t="s">
         <v>1820</v>
-      </c>
-      <c r="Q33" s="0" t="s">
-        <v>1821</v>
-      </c>
-      <c r="R33" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S33" s="0" t="s">
-        <v>1822</v>
       </c>
       <c r="T33" s="0" t="s">
         <v>28</v>
@@ -21825,28 +21828,28 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C34" s="0" t="s">
         <v>1823</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="D34" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G34" s="0" t="s">
         <v>1824</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="H34" s="0" t="s">
         <v>1825</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F34" s="0" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>1826</v>
-      </c>
-      <c r="H34" s="0" t="s">
-        <v>1827</v>
       </c>
       <c r="I34" s="0" t="s">
         <v>29</v>
@@ -21858,13 +21861,13 @@
         <v>57</v>
       </c>
       <c r="L34" s="0" t="s">
+        <v>1826</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>1827</v>
+      </c>
+      <c r="N34" s="0" t="s">
         <v>1828</v>
-      </c>
-      <c r="M34" s="0" t="s">
-        <v>1829</v>
-      </c>
-      <c r="N34" s="0" t="s">
-        <v>1830</v>
       </c>
       <c r="O34" s="0" t="s">
         <v>48</v>
@@ -21873,13 +21876,13 @@
         <v>469</v>
       </c>
       <c r="Q34" s="0" t="s">
+        <v>1829</v>
+      </c>
+      <c r="R34" s="0" t="s">
+        <v>1830</v>
+      </c>
+      <c r="S34" s="0" t="s">
         <v>1831</v>
-      </c>
-      <c r="R34" s="0" t="s">
-        <v>1832</v>
-      </c>
-      <c r="S34" s="0" t="s">
-        <v>1833</v>
       </c>
       <c r="T34" s="0" t="s">
         <v>28</v>
@@ -21887,28 +21890,28 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="0" t="s">
         <v>1834</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="E35" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F35" s="0" t="s">
         <v>1835</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>1836</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>1837</v>
       </c>
       <c r="G35" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>29</v>
@@ -21920,7 +21923,7 @@
         <v>57</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="M35" s="0" t="s">
         <v>349</v>
@@ -21932,16 +21935,16 @@
         <v>48</v>
       </c>
       <c r="P35" s="0" t="s">
+        <v>1838</v>
+      </c>
+      <c r="Q35" s="0" t="s">
+        <v>1839</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S35" s="0" t="s">
         <v>1840</v>
-      </c>
-      <c r="Q35" s="0" t="s">
-        <v>1841</v>
-      </c>
-      <c r="R35" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S35" s="0" t="s">
-        <v>1842</v>
       </c>
       <c r="T35" s="0" t="s">
         <v>28</v>
@@ -21949,28 +21952,28 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="0" t="s">
         <v>1843</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>1844</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>1845</v>
-      </c>
       <c r="E36" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G36" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="I36" s="0" t="s">
         <v>29</v>
@@ -21982,28 +21985,28 @@
         <v>57</v>
       </c>
       <c r="L36" s="0" t="s">
+        <v>1845</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>1846</v>
+      </c>
+      <c r="N36" s="0" t="s">
         <v>1847</v>
       </c>
-      <c r="M36" s="0" t="s">
+      <c r="O36" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P36" s="0" t="s">
         <v>1848</v>
       </c>
-      <c r="N36" s="0" t="s">
+      <c r="Q36" s="0" t="s">
         <v>1849</v>
       </c>
-      <c r="O36" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P36" s="0" t="s">
+      <c r="R36" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S36" s="0" t="s">
         <v>1850</v>
-      </c>
-      <c r="Q36" s="0" t="s">
-        <v>1851</v>
-      </c>
-      <c r="R36" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="S36" s="0" t="s">
-        <v>1852</v>
       </c>
       <c r="T36" s="0" t="s">
         <v>28</v>
@@ -22011,28 +22014,28 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="0" t="s">
         <v>1853</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="E37" s="0" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F37" s="0" t="s">
         <v>1854</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>1855</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>1856</v>
       </c>
       <c r="G37" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="I37" s="0" t="s">
         <v>29</v>
@@ -22044,10 +22047,10 @@
         <v>57</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N37" s="0" t="s">
         <v>70</v>
@@ -22056,16 +22059,16 @@
         <v>48</v>
       </c>
       <c r="P37" s="0" t="s">
+        <v>1858</v>
+      </c>
+      <c r="Q37" s="0" t="s">
+        <v>1859</v>
+      </c>
+      <c r="R37" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S37" s="0" t="s">
         <v>1860</v>
-      </c>
-      <c r="Q37" s="0" t="s">
-        <v>1861</v>
-      </c>
-      <c r="R37" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S37" s="0" t="s">
-        <v>1862</v>
       </c>
       <c r="T37" s="0" t="s">
         <v>28</v>
@@ -22073,10 +22076,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>28</v>
@@ -22085,16 +22088,16 @@
         <v>28</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G38" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="I38" s="0" t="s">
         <v>29</v>
@@ -22106,10 +22109,10 @@
         <v>57</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N38" s="0" t="s">
         <v>70</v>
@@ -22121,16 +22124,16 @@
         <v>187</v>
       </c>
       <c r="Q38" s="0" t="s">
+        <v>1865</v>
+      </c>
+      <c r="R38" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S38" s="0" t="s">
+        <v>1866</v>
+      </c>
+      <c r="T38" s="0" t="s">
         <v>1867</v>
-      </c>
-      <c r="R38" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S38" s="0" t="s">
-        <v>1868</v>
-      </c>
-      <c r="T38" s="0" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="39">
@@ -22138,25 +22141,25 @@
         <v>491</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G39" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="I39" s="0" t="s">
         <v>29</v>
@@ -22168,10 +22171,10 @@
         <v>57</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N39" s="0" t="s">
         <v>70</v>
@@ -22186,10 +22189,10 @@
         <v>488</v>
       </c>
       <c r="R39" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S39" s="0" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="T39" s="0" t="s">
         <v>28</v>
@@ -22200,25 +22203,25 @@
         <v>878</v>
       </c>
       <c r="B40" s="0" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F40" s="0" t="s">
         <v>1874</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>1875</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>1876</v>
       </c>
       <c r="G40" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="I40" s="0" t="s">
         <v>29</v>
@@ -22230,10 +22233,10 @@
         <v>57</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N40" s="0" t="s">
         <v>70</v>
@@ -22242,13 +22245,13 @@
         <v>48</v>
       </c>
       <c r="P40" s="0" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="Q40" s="0" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="R40" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S40" s="0" t="s">
         <v>28</v>
@@ -22259,25 +22262,25 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G41" s="0" t="s">
         <v>1881</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>1882</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>1883</v>
       </c>
       <c r="H41" s="0" t="s">
         <v>28</v>
@@ -22292,57 +22295,57 @@
         <v>57</v>
       </c>
       <c r="L41" s="0" t="s">
+        <v>1882</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>1883</v>
+      </c>
+      <c r="N41" s="0" t="s">
+        <v>1881</v>
+      </c>
+      <c r="O41" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P41" s="0" t="s">
         <v>1884</v>
       </c>
-      <c r="M41" s="0" t="s">
+      <c r="Q41" s="0" t="s">
         <v>1885</v>
       </c>
-      <c r="N41" s="0" t="s">
-        <v>1883</v>
-      </c>
-      <c r="O41" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P41" s="0" t="s">
+      <c r="R41" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S41" s="0" t="s">
         <v>1886</v>
       </c>
-      <c r="Q41" s="0" t="s">
+      <c r="T41" s="0" t="s">
         <v>1887</v>
-      </c>
-      <c r="R41" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S41" s="0" t="s">
-        <v>1888</v>
-      </c>
-      <c r="T41" s="0" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="0" t="s">
         <v>1890</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="E42" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F42" s="0" t="s">
         <v>1891</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>1892</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>1893</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>782</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="I42" s="0" t="s">
         <v>29</v>
@@ -22354,28 +22357,28 @@
         <v>57</v>
       </c>
       <c r="L42" s="0" t="s">
+        <v>1893</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>1894</v>
+      </c>
+      <c r="N42" s="0" t="s">
         <v>1895</v>
       </c>
-      <c r="M42" s="0" t="s">
+      <c r="O42" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P42" s="0" t="s">
         <v>1896</v>
       </c>
-      <c r="N42" s="0" t="s">
+      <c r="Q42" s="0" t="s">
         <v>1897</v>
       </c>
-      <c r="O42" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P42" s="0" t="s">
+      <c r="R42" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S42" s="0" t="s">
         <v>1898</v>
-      </c>
-      <c r="Q42" s="0" t="s">
-        <v>1899</v>
-      </c>
-      <c r="R42" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S42" s="0" t="s">
-        <v>1900</v>
       </c>
       <c r="T42" s="0" t="s">
         <v>28</v>
@@ -22383,40 +22386,40 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="0" t="s">
         <v>1901</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>1903</v>
-      </c>
       <c r="E43" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G43" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="I43" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J43" s="0" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="K43" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="M43" s="0" t="s">
         <v>447</v>
@@ -22428,16 +22431,16 @@
         <v>48</v>
       </c>
       <c r="P43" s="0" t="s">
+        <v>1905</v>
+      </c>
+      <c r="Q43" s="0" t="s">
+        <v>1906</v>
+      </c>
+      <c r="R43" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S43" s="0" t="s">
         <v>1907</v>
-      </c>
-      <c r="Q43" s="0" t="s">
-        <v>1908</v>
-      </c>
-      <c r="R43" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S43" s="0" t="s">
-        <v>1909</v>
       </c>
       <c r="T43" s="0" t="s">
         <v>28</v>
@@ -22448,37 +22451,37 @@
         <v>179</v>
       </c>
       <c r="B44" s="0" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D44" s="0" t="s">
         <v>1910</v>
       </c>
-      <c r="C44" s="0" t="s">
-        <v>1911</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>1912</v>
-      </c>
       <c r="E44" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G44" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="I44" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="K44" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="M44" s="0" t="s">
         <v>172</v>
@@ -22493,13 +22496,13 @@
         <v>434</v>
       </c>
       <c r="Q44" s="0" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="R44" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S44" s="0" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="T44" s="0" t="s">
         <v>28</v>
@@ -22510,37 +22513,37 @@
         <v>233</v>
       </c>
       <c r="B45" s="0" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>1917</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F45" s="0" t="s">
         <v>1918</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="0" t="s">
+      <c r="G45" s="0" t="s">
         <v>1919</v>
       </c>
-      <c r="E45" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F45" s="0" t="s">
+      <c r="H45" s="0" t="s">
         <v>1920</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="I45" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J45" s="0" t="s">
         <v>1921</v>
-      </c>
-      <c r="H45" s="0" t="s">
-        <v>1922</v>
-      </c>
-      <c r="I45" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J45" s="0" t="s">
-        <v>1923</v>
       </c>
       <c r="K45" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="M45" s="0" t="s">
         <v>908</v>
@@ -22552,16 +22555,16 @@
         <v>48</v>
       </c>
       <c r="P45" s="0" t="s">
+        <v>1923</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>1924</v>
+      </c>
+      <c r="R45" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S45" s="0" t="s">
         <v>1925</v>
-      </c>
-      <c r="Q45" s="0" t="s">
-        <v>1926</v>
-      </c>
-      <c r="R45" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S45" s="0" t="s">
-        <v>1927</v>
       </c>
       <c r="T45" s="0" t="s">
         <v>28</v>
@@ -22569,61 +22572,61 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="0" t="s">
         <v>1928</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>1929</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>1930</v>
-      </c>
       <c r="E46" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G46" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H46" s="0" t="s">
+        <v>1929</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>1854</v>
+      </c>
+      <c r="K46" s="0" t="s">
+        <v>1930</v>
+      </c>
+      <c r="L46" s="0" t="s">
         <v>1931</v>
       </c>
-      <c r="I46" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J46" s="0" t="s">
-        <v>1856</v>
-      </c>
-      <c r="K46" s="0" t="s">
+      <c r="M46" s="0" t="s">
         <v>1932</v>
       </c>
-      <c r="L46" s="0" t="s">
+      <c r="N46" s="0" t="s">
         <v>1933</v>
       </c>
-      <c r="M46" s="0" t="s">
+      <c r="O46" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P46" s="0" t="s">
         <v>1934</v>
       </c>
-      <c r="N46" s="0" t="s">
+      <c r="Q46" s="0" t="s">
         <v>1935</v>
       </c>
-      <c r="O46" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P46" s="0" t="s">
+      <c r="R46" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S46" s="0" t="s">
         <v>1936</v>
-      </c>
-      <c r="Q46" s="0" t="s">
-        <v>1937</v>
-      </c>
-      <c r="R46" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S46" s="0" t="s">
-        <v>1938</v>
       </c>
       <c r="T46" s="0" t="s">
         <v>28</v>
@@ -22631,61 +22634,61 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="0" t="s">
         <v>1939</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="E47" s="0" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="0" t="s">
         <v>1940</v>
       </c>
-      <c r="C47" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="0" t="s">
+      <c r="H47" s="0" t="s">
         <v>1941</v>
       </c>
-      <c r="E47" s="0" t="s">
-        <v>1778</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47" s="0" t="s">
-        <v>1942</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>1943</v>
-      </c>
       <c r="I47" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="K47" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L47" s="0" t="s">
+        <v>1942</v>
+      </c>
+      <c r="M47" s="0" t="s">
+        <v>1943</v>
+      </c>
+      <c r="N47" s="0" t="s">
+        <v>1940</v>
+      </c>
+      <c r="O47" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P47" s="0" t="s">
+        <v>1607</v>
+      </c>
+      <c r="Q47" s="0" t="s">
         <v>1944</v>
       </c>
-      <c r="M47" s="0" t="s">
+      <c r="R47" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S47" s="0" t="s">
         <v>1945</v>
-      </c>
-      <c r="N47" s="0" t="s">
-        <v>1942</v>
-      </c>
-      <c r="O47" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P47" s="0" t="s">
-        <v>1609</v>
-      </c>
-      <c r="Q47" s="0" t="s">
-        <v>1946</v>
-      </c>
-      <c r="R47" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="S47" s="0" t="s">
-        <v>1947</v>
       </c>
       <c r="T47" s="0" t="s">
         <v>28</v>
@@ -22696,25 +22699,25 @@
         <v>752</v>
       </c>
       <c r="B48" s="0" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F48" s="0" t="s">
         <v>1948</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>1949</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>1950</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="I48" s="0" t="s">
         <v>29</v>
@@ -22726,7 +22729,7 @@
         <v>57</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="M48" s="0" t="s">
         <v>427</v>
@@ -22747,7 +22750,7 @@
         <v>28</v>
       </c>
       <c r="S48" s="0" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="T48" s="0" t="s">
         <v>28</v>
@@ -22755,61 +22758,61 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="0" t="s">
         <v>1954</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>1955</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>1956</v>
-      </c>
       <c r="E49" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>728</v>
       </c>
       <c r="G49" s="0" t="s">
+        <v>1955</v>
+      </c>
+      <c r="H49" s="0" t="s">
+        <v>1956</v>
+      </c>
+      <c r="I49" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" s="0" t="s">
         <v>1957</v>
-      </c>
-      <c r="H49" s="0" t="s">
-        <v>1958</v>
-      </c>
-      <c r="I49" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J49" s="0" t="s">
-        <v>1959</v>
       </c>
       <c r="K49" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L49" s="0" t="s">
+        <v>1958</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>1959</v>
+      </c>
+      <c r="N49" s="0" t="s">
+        <v>1955</v>
+      </c>
+      <c r="O49" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P49" s="0" t="s">
         <v>1960</v>
       </c>
-      <c r="M49" s="0" t="s">
+      <c r="Q49" s="0" t="s">
         <v>1961</v>
       </c>
-      <c r="N49" s="0" t="s">
-        <v>1957</v>
-      </c>
-      <c r="O49" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P49" s="0" t="s">
+      <c r="R49" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S49" s="0" t="s">
         <v>1962</v>
-      </c>
-      <c r="Q49" s="0" t="s">
-        <v>1963</v>
-      </c>
-      <c r="R49" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S49" s="0" t="s">
-        <v>1964</v>
       </c>
       <c r="T49" s="0" t="s">
         <v>28</v>
@@ -22817,10 +22820,10 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>28</v>
@@ -22829,7 +22832,7 @@
         <v>28</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F50" s="0" t="s">
         <v>728</v>
@@ -22838,19 +22841,19 @@
         <v>70</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="I50" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="K50" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="M50" s="0" t="s">
         <v>1220</v>
@@ -22862,13 +22865,13 @@
         <v>48</v>
       </c>
       <c r="P50" s="0" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="Q50" s="0" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="R50" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S50" s="0" t="s">
         <v>28</v>
@@ -22882,7 +22885,7 @@
         <v>1362</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>1072</v>
@@ -22891,16 +22894,16 @@
         <v>1073</v>
       </c>
       <c r="E51" s="0" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="0" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H51" s="0" t="s">
         <v>1972</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G51" s="0" t="s">
-        <v>1973</v>
-      </c>
-      <c r="H51" s="0" t="s">
-        <v>1974</v>
       </c>
       <c r="I51" s="0" t="s">
         <v>29</v>
@@ -22912,10 +22915,10 @@
         <v>57</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="N51" s="0" t="s">
         <v>1076</v>
@@ -22924,13 +22927,13 @@
         <v>48</v>
       </c>
       <c r="P51" s="0" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="Q51" s="0" t="s">
         <v>1070</v>
       </c>
       <c r="R51" s="0" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="S51" s="0" t="s">
         <v>1077</v>
@@ -22941,40 +22944,40 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="0" t="s">
         <v>1979</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="E52" s="0" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F52" s="0" t="s">
         <v>1980</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>1981</v>
-      </c>
-      <c r="E52" s="0" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F52" s="0" t="s">
-        <v>1982</v>
       </c>
       <c r="G52" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="I52" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="K52" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="M52" s="0" t="s">
         <v>447</v>
@@ -22992,10 +22995,10 @@
         <v>28</v>
       </c>
       <c r="R52" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S52" s="0" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="T52" s="0" t="s">
         <v>28</v>
@@ -23006,7 +23009,7 @@
         <v>1254</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>28</v>
@@ -23015,28 +23018,28 @@
         <v>28</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G53" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="I53" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="K53" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="M53" s="0" t="s">
         <v>456</v>
@@ -23048,13 +23051,13 @@
         <v>48</v>
       </c>
       <c r="P53" s="0" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="Q53" s="0" t="s">
         <v>1251</v>
       </c>
       <c r="R53" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S53" s="0" t="s">
         <v>1257</v>
@@ -23068,25 +23071,25 @@
         <v>110</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G54" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="I54" s="0" t="s">
         <v>29</v>
@@ -23127,28 +23130,28 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C55" s="0" t="s">
         <v>1995</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="D55" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F55" s="0" t="s">
         <v>1996</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>1998</v>
       </c>
       <c r="G55" s="0" t="s">
         <v>47</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="I55" s="0" t="s">
         <v>29</v>
@@ -23160,7 +23163,7 @@
         <v>834</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="M55" s="0" t="s">
         <v>349</v>
@@ -23175,13 +23178,13 @@
         <v>1441</v>
       </c>
       <c r="Q55" s="0" t="s">
+        <v>1999</v>
+      </c>
+      <c r="R55" s="0" t="s">
+        <v>2000</v>
+      </c>
+      <c r="S55" s="0" t="s">
         <v>2001</v>
-      </c>
-      <c r="R55" s="0" t="s">
-        <v>2002</v>
-      </c>
-      <c r="S55" s="0" t="s">
-        <v>2003</v>
       </c>
       <c r="T55" s="0" t="s">
         <v>28</v>
@@ -23192,25 +23195,25 @@
         <v>635</v>
       </c>
       <c r="B56" s="0" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="0" t="s">
         <v>2004</v>
       </c>
-      <c r="C56" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>2005</v>
-      </c>
-      <c r="E56" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>2006</v>
-      </c>
       <c r="H56" s="0" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>29</v>
@@ -23222,13 +23225,13 @@
         <v>57</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="O56" s="0" t="s">
         <v>48</v>
@@ -23237,13 +23240,13 @@
         <v>918</v>
       </c>
       <c r="Q56" s="0" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="R56" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S56" s="0" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="T56" s="0" t="s">
         <v>28</v>
@@ -23251,10 +23254,10 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>28</v>
@@ -23263,7 +23266,7 @@
         <v>28</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>28</v>
@@ -23272,19 +23275,19 @@
         <v>70</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="K57" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="M57" s="0" t="s">
         <v>172</v>
@@ -23296,16 +23299,16 @@
         <v>48</v>
       </c>
       <c r="P57" s="0" t="s">
+        <v>2014</v>
+      </c>
+      <c r="Q57" s="0" t="s">
+        <v>2015</v>
+      </c>
+      <c r="R57" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="S57" s="0" t="s">
         <v>2016</v>
-      </c>
-      <c r="Q57" s="0" t="s">
-        <v>2017</v>
-      </c>
-      <c r="R57" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="S57" s="0" t="s">
-        <v>2018</v>
       </c>
       <c r="T57" s="0" t="s">
         <v>28</v>
@@ -23316,40 +23319,40 @@
         <v>99</v>
       </c>
       <c r="B58" s="0" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H58" s="0" t="s">
+        <v>2018</v>
+      </c>
+      <c r="I58" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J58" s="0" t="s">
         <v>2019</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F58" s="0" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G58" s="0" t="s">
-        <v>1921</v>
-      </c>
-      <c r="H58" s="0" t="s">
-        <v>2020</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J58" s="0" t="s">
-        <v>2021</v>
       </c>
       <c r="K58" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N58" s="0" t="s">
         <v>70</v>
@@ -23378,25 +23381,25 @@
         <v>1367</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G59" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="I59" s="0" t="s">
         <v>29</v>
@@ -23408,10 +23411,10 @@
         <v>57</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="N59" s="0" t="s">
         <v>70</v>
@@ -23420,16 +23423,16 @@
         <v>48</v>
       </c>
       <c r="P59" s="0" t="s">
+        <v>2026</v>
+      </c>
+      <c r="Q59" s="0" t="s">
+        <v>2027</v>
+      </c>
+      <c r="R59" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S59" s="0" t="s">
         <v>2028</v>
-      </c>
-      <c r="Q59" s="0" t="s">
-        <v>2029</v>
-      </c>
-      <c r="R59" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S59" s="0" t="s">
-        <v>2030</v>
       </c>
       <c r="T59" s="0" t="s">
         <v>28</v>
@@ -23440,7 +23443,7 @@
         <v>77</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>28</v>
@@ -23449,16 +23452,16 @@
         <v>706</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="I60" s="0" t="s">
         <v>29</v>
@@ -23470,10 +23473,10 @@
         <v>57</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="M60" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N60" s="0" t="s">
         <v>70</v>
@@ -23482,16 +23485,16 @@
         <v>48</v>
       </c>
       <c r="P60" s="0" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="Q60" s="0" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="R60" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S60" s="0" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="T60" s="0" t="s">
         <v>28</v>
@@ -23499,28 +23502,28 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F61" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="0" t="s">
         <v>2037</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="H61" s="0" t="s">
         <v>2038</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="0" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F61" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61" s="0" t="s">
-        <v>2039</v>
-      </c>
-      <c r="H61" s="0" t="s">
-        <v>2040</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>29</v>
@@ -23532,13 +23535,13 @@
         <v>57</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="O61" s="0" t="s">
         <v>48</v>
@@ -23547,42 +23550,42 @@
         <v>231</v>
       </c>
       <c r="Q61" s="0" t="s">
+        <v>2041</v>
+      </c>
+      <c r="R61" s="0" t="s">
+        <v>2042</v>
+      </c>
+      <c r="S61" s="0" t="s">
         <v>2043</v>
       </c>
-      <c r="R61" s="0" t="s">
+      <c r="T61" s="0" t="s">
         <v>2044</v>
-      </c>
-      <c r="S61" s="0" t="s">
-        <v>2045</v>
-      </c>
-      <c r="T61" s="0" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="0" t="s">
         <v>2047</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>2048</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D62" s="0" t="s">
-        <v>2049</v>
-      </c>
       <c r="E62" s="0" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="G62" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>29</v>
@@ -23594,7 +23597,7 @@
         <v>57</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="M62" s="0" t="s">
         <v>69</v>
@@ -23606,16 +23609,16 @@
         <v>48</v>
       </c>
       <c r="P62" s="0" t="s">
+        <v>2049</v>
+      </c>
+      <c r="Q62" s="0" t="s">
+        <v>2050</v>
+      </c>
+      <c r="R62" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S62" s="0" t="s">
         <v>2051</v>
-      </c>
-      <c r="Q62" s="0" t="s">
-        <v>2052</v>
-      </c>
-      <c r="R62" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S62" s="0" t="s">
-        <v>2053</v>
       </c>
       <c r="T62" s="0" t="s">
         <v>28</v>
@@ -23623,10 +23626,10 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>28</v>
@@ -23635,7 +23638,7 @@
         <v>28</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>28</v>
@@ -23644,7 +23647,7 @@
         <v>992</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>29</v>
@@ -23656,7 +23659,7 @@
         <v>510</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="M63" s="0" t="s">
         <v>262</v>
@@ -23668,13 +23671,13 @@
         <v>48</v>
       </c>
       <c r="P63" s="0" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="Q63" s="0" t="s">
         <v>617</v>
       </c>
       <c r="R63" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S63" s="0" t="s">
         <v>1383</v>
@@ -23688,25 +23691,25 @@
         <v>311</v>
       </c>
       <c r="B64" s="0" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F64" s="0" t="s">
         <v>2059</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D64" s="0" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E64" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F64" s="0" t="s">
-        <v>2061</v>
       </c>
       <c r="G64" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>29</v>
@@ -23718,10 +23721,10 @@
         <v>57</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="N64" s="0" t="s">
         <v>70</v>
@@ -23730,16 +23733,16 @@
         <v>48</v>
       </c>
       <c r="P64" s="0" t="s">
+        <v>2063</v>
+      </c>
+      <c r="Q64" s="0" t="s">
+        <v>2064</v>
+      </c>
+      <c r="R64" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S64" s="0" t="s">
         <v>2065</v>
-      </c>
-      <c r="Q64" s="0" t="s">
-        <v>2066</v>
-      </c>
-      <c r="R64" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S64" s="0" t="s">
-        <v>2067</v>
       </c>
       <c r="T64" s="0" t="s">
         <v>28</v>
@@ -23747,43 +23750,43 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="0" t="s">
         <v>2068</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="E65" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="0" t="s">
         <v>2069</v>
       </c>
-      <c r="C65" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" s="0" t="s">
+      <c r="I65" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J65" s="0" t="s">
         <v>2070</v>
       </c>
-      <c r="E65" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="F65" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="H65" s="0" t="s">
+      <c r="K65" s="0" t="s">
         <v>2071</v>
       </c>
-      <c r="I65" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J65" s="0" t="s">
+      <c r="L65" s="0" t="s">
         <v>2072</v>
       </c>
-      <c r="K65" s="0" t="s">
+      <c r="M65" s="0" t="s">
         <v>2073</v>
-      </c>
-      <c r="L65" s="0" t="s">
-        <v>2074</v>
-      </c>
-      <c r="M65" s="0" t="s">
-        <v>2075</v>
       </c>
       <c r="N65" s="0" t="s">
         <v>28</v>
@@ -23812,37 +23815,37 @@
         <v>1145</v>
       </c>
       <c r="B66" s="0" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F66" s="0" t="s">
         <v>2076</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="0" t="s">
-        <v>2077</v>
-      </c>
-      <c r="E66" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F66" s="0" t="s">
-        <v>2078</v>
       </c>
       <c r="G66" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="K66" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="M66" s="0" t="s">
         <v>402</v>
@@ -23854,16 +23857,16 @@
         <v>48</v>
       </c>
       <c r="P66" s="0" t="s">
+        <v>2080</v>
+      </c>
+      <c r="Q66" s="0" t="s">
+        <v>2081</v>
+      </c>
+      <c r="R66" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S66" s="0" t="s">
         <v>2082</v>
-      </c>
-      <c r="Q66" s="0" t="s">
-        <v>2083</v>
-      </c>
-      <c r="R66" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S66" s="0" t="s">
-        <v>2084</v>
       </c>
       <c r="T66" s="0" t="s">
         <v>28</v>
@@ -23874,25 +23877,25 @@
         <v>42</v>
       </c>
       <c r="B67" s="0" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F67" s="0" t="s">
         <v>2085</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>2086</v>
-      </c>
-      <c r="E67" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F67" s="0" t="s">
-        <v>2087</v>
       </c>
       <c r="G67" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="I67" s="0" t="s">
         <v>29</v>
@@ -23904,7 +23907,7 @@
         <v>57</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="M67" s="0" t="s">
         <v>501</v>
@@ -23916,16 +23919,16 @@
         <v>48</v>
       </c>
       <c r="P67" s="0" t="s">
+        <v>2088</v>
+      </c>
+      <c r="Q67" s="0" t="s">
+        <v>2089</v>
+      </c>
+      <c r="R67" s="0" t="s">
+        <v>1568</v>
+      </c>
+      <c r="S67" s="0" t="s">
         <v>2090</v>
-      </c>
-      <c r="Q67" s="0" t="s">
-        <v>2091</v>
-      </c>
-      <c r="R67" s="0" t="s">
-        <v>1570</v>
-      </c>
-      <c r="S67" s="0" t="s">
-        <v>2092</v>
       </c>
       <c r="T67" s="0" t="s">
         <v>28</v>
@@ -23936,7 +23939,7 @@
         <v>1350</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>28</v>
@@ -23945,7 +23948,7 @@
         <v>28</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F68" s="0" t="s">
         <v>28</v>
@@ -23954,7 +23957,7 @@
         <v>782</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="I68" s="0" t="s">
         <v>29</v>
@@ -23966,13 +23969,13 @@
         <v>57</v>
       </c>
       <c r="L68" s="0" t="s">
+        <v>2093</v>
+      </c>
+      <c r="M68" s="0" t="s">
+        <v>2094</v>
+      </c>
+      <c r="N68" s="0" t="s">
         <v>2095</v>
-      </c>
-      <c r="M68" s="0" t="s">
-        <v>2096</v>
-      </c>
-      <c r="N68" s="0" t="s">
-        <v>2097</v>
       </c>
       <c r="O68" s="0" t="s">
         <v>48</v>
@@ -23984,7 +23987,7 @@
         <v>1348</v>
       </c>
       <c r="R68" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S68" s="0" t="s">
         <v>1356</v>
@@ -23998,40 +24001,40 @@
         <v>771</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="I69" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="K69" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="M69" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N69" s="0" t="s">
         <v>70</v>
@@ -24043,10 +24046,10 @@
         <v>769</v>
       </c>
       <c r="Q69" s="0" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="R69" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S69" s="0" t="s">
         <v>227</v>
@@ -24060,25 +24063,25 @@
         <v>779</v>
       </c>
       <c r="B70" s="0" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H70" s="0" t="s">
         <v>2102</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" s="0" t="s">
-        <v>2103</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F70" s="0" t="s">
-        <v>1733</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>1709</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>2104</v>
       </c>
       <c r="I70" s="0" t="s">
         <v>29</v>
@@ -24090,13 +24093,13 @@
         <v>57</v>
       </c>
       <c r="L70" s="0" t="s">
+        <v>2103</v>
+      </c>
+      <c r="M70" s="0" t="s">
+        <v>2104</v>
+      </c>
+      <c r="N70" s="0" t="s">
         <v>2105</v>
-      </c>
-      <c r="M70" s="0" t="s">
-        <v>2106</v>
-      </c>
-      <c r="N70" s="0" t="s">
-        <v>2107</v>
       </c>
       <c r="O70" s="0" t="s">
         <v>48</v>
@@ -24105,13 +24108,13 @@
         <v>912</v>
       </c>
       <c r="Q70" s="0" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="R70" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S70" s="0" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="T70" s="0" t="s">
         <v>28</v>
@@ -24119,28 +24122,28 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>2110</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>2111</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="0" t="s">
-        <v>2112</v>
-      </c>
       <c r="E71" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="G71" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>29</v>
@@ -24152,7 +24155,7 @@
         <v>57</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="M71" s="0" t="s">
         <v>1060</v>
@@ -24170,10 +24173,10 @@
         <v>407</v>
       </c>
       <c r="R71" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S71" s="0" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="T71" s="0" t="s">
         <v>28</v>
@@ -24181,28 +24184,28 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" s="0" t="s">
         <v>2116</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="E72" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F72" s="0" t="s">
         <v>2117</v>
-      </c>
-      <c r="C72" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" s="0" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E72" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F72" s="0" t="s">
-        <v>2119</v>
       </c>
       <c r="G72" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="I72" s="0" t="s">
         <v>29</v>
@@ -24214,7 +24217,7 @@
         <v>357</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="M72" s="0" t="s">
         <v>1220</v>
@@ -24226,16 +24229,16 @@
         <v>48</v>
       </c>
       <c r="P72" s="0" t="s">
+        <v>2120</v>
+      </c>
+      <c r="Q72" s="0" t="s">
+        <v>2121</v>
+      </c>
+      <c r="R72" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S72" s="0" t="s">
         <v>2122</v>
-      </c>
-      <c r="Q72" s="0" t="s">
-        <v>2123</v>
-      </c>
-      <c r="R72" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S72" s="0" t="s">
-        <v>2124</v>
       </c>
       <c r="T72" s="0" t="s">
         <v>28</v>
@@ -24246,25 +24249,25 @@
         <v>198</v>
       </c>
       <c r="B73" s="0" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F73" s="0" t="s">
+        <v>2124</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H73" s="0" t="s">
         <v>2125</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D73" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F73" s="0" t="s">
-        <v>2126</v>
-      </c>
-      <c r="G73" s="0" t="s">
-        <v>1687</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>2127</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>29</v>
@@ -24276,13 +24279,13 @@
         <v>57</v>
       </c>
       <c r="L73" s="0" t="s">
+        <v>2126</v>
+      </c>
+      <c r="M73" s="0" t="s">
+        <v>2127</v>
+      </c>
+      <c r="N73" s="0" t="s">
         <v>2128</v>
-      </c>
-      <c r="M73" s="0" t="s">
-        <v>2129</v>
-      </c>
-      <c r="N73" s="0" t="s">
-        <v>2130</v>
       </c>
       <c r="O73" s="0" t="s">
         <v>48</v>
@@ -24294,7 +24297,7 @@
         <v>266</v>
       </c>
       <c r="R73" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S73" s="0" t="s">
         <v>28</v>
@@ -24305,28 +24308,28 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="0" t="s">
         <v>2131</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>2132</v>
-      </c>
-      <c r="C74" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="0" t="s">
-        <v>2133</v>
-      </c>
       <c r="E74" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="G74" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="I74" s="0" t="s">
         <v>29</v>
@@ -24338,7 +24341,7 @@
         <v>410</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="M74" s="0" t="s">
         <v>375</v>
@@ -24353,10 +24356,10 @@
         <v>370</v>
       </c>
       <c r="Q74" s="0" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
       <c r="R74" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S74" s="0" t="s">
         <v>1292</v>
@@ -24370,37 +24373,37 @@
         <v>454</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>28</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="I75" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J75" s="0" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>161</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="M75" s="0" t="s">
         <v>529</v>
@@ -24415,13 +24418,13 @@
         <v>842</v>
       </c>
       <c r="Q75" s="0" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="R75" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="T75" s="0" t="s">
         <v>28</v>
@@ -24432,7 +24435,7 @@
         <v>464</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>28</v>
@@ -24441,28 +24444,28 @@
         <v>546</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="G76" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J76" s="0" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="K76" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="M76" s="0" t="s">
         <v>439</v>
@@ -24474,13 +24477,13 @@
         <v>48</v>
       </c>
       <c r="P76" s="0" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="Q76" s="0" t="s">
         <v>461</v>
       </c>
       <c r="R76" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S76" s="0" t="s">
         <v>465</v>
@@ -24491,10 +24494,10 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>28</v>
@@ -24503,16 +24506,16 @@
         <v>28</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="G77" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="I77" s="0" t="s">
         <v>29</v>
@@ -24524,7 +24527,7 @@
         <v>57</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="M77" s="0" t="s">
         <v>456</v>
@@ -24539,13 +24542,13 @@
         <v>310</v>
       </c>
       <c r="Q77" s="0" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="R77" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S77" s="0" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="T77" s="0" t="s">
         <v>28</v>
@@ -24556,7 +24559,7 @@
         <v>1498</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>28</v>
@@ -24565,16 +24568,16 @@
         <v>28</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="G78" s="0" t="s">
         <v>28</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>29</v>
@@ -24586,25 +24589,25 @@
         <v>57</v>
       </c>
       <c r="L78" s="0" t="s">
+        <v>2155</v>
+      </c>
+      <c r="M78" s="0" t="s">
+        <v>2156</v>
+      </c>
+      <c r="N78" s="0" t="s">
         <v>2157</v>
       </c>
-      <c r="M78" s="0" t="s">
+      <c r="O78" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="P78" s="0" t="s">
         <v>2158</v>
       </c>
-      <c r="N78" s="0" t="s">
+      <c r="Q78" s="0" t="s">
         <v>2159</v>
       </c>
-      <c r="O78" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="P78" s="0" t="s">
-        <v>2160</v>
-      </c>
-      <c r="Q78" s="0" t="s">
-        <v>2161</v>
-      </c>
       <c r="R78" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S78" s="0" t="s">
         <v>1499</v>
@@ -24615,10 +24618,10 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>28</v>
@@ -24627,16 +24630,16 @@
         <v>28</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="G79" s="0" t="s">
         <v>992</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>29</v>
@@ -24660,13 +24663,13 @@
         <v>48</v>
       </c>
       <c r="P79" s="0" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="Q79" s="0" t="s">
         <v>988</v>
       </c>
       <c r="R79" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S79" s="0" t="s">
         <v>993</v>
@@ -24677,28 +24680,28 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" s="0" t="s">
         <v>2166</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="E80" s="0" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F80" s="0" t="s">
         <v>2167</v>
       </c>
-      <c r="C80" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D80" s="0" t="s">
+      <c r="G80" s="0" t="s">
         <v>2168</v>
       </c>
-      <c r="E80" s="0" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F80" s="0" t="s">
-        <v>2169</v>
-      </c>
-      <c r="G80" s="0" t="s">
-        <v>2170</v>
-      </c>
       <c r="H80" s="0" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="I80" s="0" t="s">
         <v>29</v>
@@ -24710,13 +24713,13 @@
         <v>57</v>
       </c>
       <c r="L80" s="0" t="s">
+        <v>2126</v>
+      </c>
+      <c r="M80" s="0" t="s">
+        <v>2127</v>
+      </c>
+      <c r="N80" s="0" t="s">
         <v>2128</v>
-      </c>
-      <c r="M80" s="0" t="s">
-        <v>2129</v>
-      </c>
-      <c r="N80" s="0" t="s">
-        <v>2130</v>
       </c>
       <c r="O80" s="0" t="s">
         <v>48</v>
@@ -24728,10 +24731,10 @@
         <v>266</v>
       </c>
       <c r="R80" s="0" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="S80" s="0" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="T80" s="0" t="s">
         <v>28</v>
@@ -24739,40 +24742,40 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="0" t="s">
         <v>2172</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="E81" s="0" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F81" s="0" t="s">
         <v>2173</v>
-      </c>
-      <c r="C81" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D81" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" s="0" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F81" s="0" t="s">
-        <v>2174</v>
       </c>
       <c r="G81" s="0" t="s">
         <v>70</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="I81" s="0" t="s">
         <v>29</v>
       </c>
       <c r="J81" s="0" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="K81" s="0" t="s">
         <v>57</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="M81" s="0" t="s">
         <v>69</v>
@@ -24784,16 +24787,16 @@
         <v>1514</v>
       </c>
       <c r="P81" s="0" t="s">
+        <v>2176</v>
+      </c>
+      <c r="Q81" s="0" t="s">
         <v>2177</v>
       </c>
-      <c r="Q81" s="0" t="s">
+      <c r="R81" s="0" t="s">
+        <v>1558</v>
+      </c>
+      <c r="S81" s="0" t="s">
         <v>2178</v>
-      </c>
-      <c r="R81" s="0" t="s">
-        <v>1560</v>
-      </c>
-      <c r="S81" s="0" t="s">
-        <v>2179</v>
       </c>
       <c r="T81" s="0" t="s">
         <v>28</v>
@@ -24801,19 +24804,19 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B82" s="0" t="s">
         <v>2180</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="C82" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="0" t="s">
         <v>2181</v>
       </c>
-      <c r="C82" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="E82" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F82" s="0" t="s">
         <v>2182</v>
@@ -24837,7 +24840,7 @@
         <v>2184</v>
       </c>
       <c r="M82" s="0" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="N82" s="0" t="s">
         <v>70</v>
@@ -24852,7 +24855,7 @@
         <v>1508</v>
       </c>
       <c r="R82" s="0" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="S82" s="0" t="s">
         <v>1515</v>
@@ -24872,19 +24875,19 @@
         <v>28</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>28</v>
+        <v>2187</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>28</v>
+        <v>2124</v>
       </c>
       <c r="G83" s="0" t="s">
         <v>1011</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>29</v>
@@ -24896,7 +24899,7 @@
         <v>57</v>
       </c>
       <c r="L83" s="0" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="M83" s="0" t="s">
         <v>1010</v>
@@ -24908,19 +24911,19 @@
         <v>1514</v>
       </c>
       <c r="P83" s="0" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="Q83" s="0" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="R83" s="0" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="S83" s="0" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="T83" s="0" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
     </row>
   </sheetData>
